--- a/BASE/DADOS_CONDOMINIOS.xlsx
+++ b/BASE/DADOS_CONDOMINIOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Wallpaper\NF GW\NF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36A32CD-6472-4FD5-931B-E4F6CDDBF01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F6BDE2-70B2-40FB-A631-D069774A69CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{06283720-90B9-47BF-AEF6-ACB6BB5B8FC8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{06283720-90B9-47BF-AEF6-ACB6BB5B8FC8}"/>
   </bookViews>
   <sheets>
     <sheet name="COND" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="687">
   <si>
     <t xml:space="preserve">MODESTO STARLING </t>
   </si>
@@ -314,9 +314,6 @@
     <t xml:space="preserve">SENHOR DO BONFIM </t>
   </si>
   <si>
-    <t xml:space="preserve">SAN ROMAN </t>
-  </si>
-  <si>
     <t>ARTHUR AUGUSTO</t>
   </si>
   <si>
@@ -2079,6 +2076,27 @@
   </si>
   <si>
     <t>17.642.214/0001-64</t>
+  </si>
+  <si>
+    <t>PRESIDENTE JUCELINO</t>
+  </si>
+  <si>
+    <t>02.464.572/0001-57</t>
+  </si>
+  <si>
+    <t>ALICE MOURA</t>
+  </si>
+  <si>
+    <t>25.569.351/0001-49</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>16.647.959/0001-53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAINT ROMAN </t>
   </si>
 </sst>
 </file>
@@ -2332,10 +2350,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8E96608-A336-487B-84FC-74891340A52C}" name="Tabela1" displayName="Tabela1" ref="A1:D337" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D337" xr:uid="{E8E96608-A336-487B-84FC-74891340A52C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D337">
-    <sortCondition ref="A1:A337"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8E96608-A336-487B-84FC-74891340A52C}" name="Tabela1" displayName="Tabela1" ref="A1:D340" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D340" xr:uid="{E8E96608-A336-487B-84FC-74891340A52C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D340">
+    <sortCondition ref="A1:A340"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{DC7CB960-927B-404F-9BFD-7EB561BE08EF}" name="COD" dataDxfId="3"/>
@@ -2644,7 +2662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B40F633-FF22-4F2F-A96C-46A2C55719BF}">
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H340"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="5"/>
@@ -2655,16 +2673,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2675,10 +2693,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,13 +2704,13 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2703,10 +2721,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2717,10 +2735,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2731,10 +2749,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2745,10 +2763,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2756,13 +2774,13 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>567</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2770,13 +2788,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>569</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2784,13 +2802,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>565</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>560</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2801,10 +2819,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2815,10 +2833,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2829,10 +2847,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2843,10 +2861,10 @@
         <v>8</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2857,10 +2875,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2871,10 +2889,10 @@
         <v>10</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2882,13 +2900,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>571</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>564</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2899,10 +2917,10 @@
         <v>11</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2913,10 +2931,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2924,13 +2942,13 @@
         <v>47</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>573</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>549</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2941,10 +2959,10 @@
         <v>13</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2955,10 +2973,10 @@
         <v>14</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2969,10 +2987,10 @@
         <v>15</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2983,10 +3001,10 @@
         <v>16</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2997,10 +3015,10 @@
         <v>17</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3011,10 +3029,10 @@
         <v>18</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3025,10 +3043,10 @@
         <v>19</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3039,10 +3057,10 @@
         <v>20</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3050,13 +3068,13 @@
         <v>73</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3064,13 +3082,13 @@
         <v>74</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3081,10 +3099,10 @@
         <v>21</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3095,10 +3113,10 @@
         <v>22</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3109,10 +3127,10 @@
         <v>23</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3123,10 +3141,10 @@
         <v>24</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3137,10 +3155,10 @@
         <v>25</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3151,10 +3169,10 @@
         <v>26</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3165,10 +3183,10 @@
         <v>27</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3179,10 +3197,10 @@
         <v>28</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3193,10 +3211,10 @@
         <v>29</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3204,13 +3222,13 @@
         <v>110</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3221,10 +3239,10 @@
         <v>30</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3235,10 +3253,10 @@
         <v>31</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3248,11 +3266,11 @@
       <c r="B43" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>564</v>
+      <c r="C43" s="11" t="s">
+        <v>546</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3263,10 +3281,10 @@
         <v>33</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3277,10 +3295,10 @@
         <v>34</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3291,10 +3309,10 @@
         <v>35</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3305,10 +3323,10 @@
         <v>36</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3319,10 +3337,10 @@
         <v>37</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3330,13 +3348,13 @@
         <v>124</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3347,10 +3365,10 @@
         <v>38</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3361,10 +3379,10 @@
         <v>39</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3375,10 +3393,10 @@
         <v>40</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3389,10 +3407,10 @@
         <v>41</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3400,13 +3418,13 @@
         <v>139</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>575</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3414,13 +3432,13 @@
         <v>142</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>582</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>547</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3431,10 +3449,10 @@
         <v>42</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3445,10 +3463,10 @@
         <v>43</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3459,10 +3477,10 @@
         <v>44</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3470,13 +3488,13 @@
         <v>164</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3487,10 +3505,10 @@
         <v>45</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3501,10 +3519,10 @@
         <v>46</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3515,10 +3533,10 @@
         <v>47</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3529,10 +3547,10 @@
         <v>48</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3540,13 +3558,13 @@
         <v>176</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3554,13 +3572,13 @@
         <v>179</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3571,10 +3589,10 @@
         <v>49</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3585,10 +3603,10 @@
         <v>50</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3599,10 +3617,10 @@
         <v>51</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3613,10 +3631,10 @@
         <v>52</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3627,10 +3645,10 @@
         <v>53</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3641,10 +3659,10 @@
         <v>54</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3655,10 +3673,10 @@
         <v>55</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3669,10 +3687,10 @@
         <v>56</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3683,10 +3701,10 @@
         <v>57</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3697,10 +3715,10 @@
         <v>58</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3708,13 +3726,13 @@
         <v>219</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3725,10 +3743,10 @@
         <v>59</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3739,10 +3757,10 @@
         <v>60</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3753,10 +3771,10 @@
         <v>61</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3767,10 +3785,10 @@
         <v>62</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3781,10 +3799,10 @@
         <v>63</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3792,13 +3810,13 @@
         <v>236</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3809,10 +3827,10 @@
         <v>64</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3820,13 +3838,13 @@
         <v>242</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3834,13 +3852,13 @@
         <v>245</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3851,10 +3869,10 @@
         <v>65</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3862,13 +3880,13 @@
         <v>248</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3879,10 +3897,10 @@
         <v>66</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3893,10 +3911,10 @@
         <v>67</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3907,10 +3925,10 @@
         <v>68</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3918,13 +3936,13 @@
         <v>274</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>589</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3935,10 +3953,10 @@
         <v>69</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3949,10 +3967,10 @@
         <v>70</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -3960,13 +3978,13 @@
         <v>278</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3977,10 +3995,10 @@
         <v>71</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3991,10 +4009,10 @@
         <v>72</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -4005,10 +4023,10 @@
         <v>73</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -4016,13 +4034,13 @@
         <v>290</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -4033,10 +4051,10 @@
         <v>74</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -4044,13 +4062,13 @@
         <v>294</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -4061,10 +4079,10 @@
         <v>75</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -4075,10 +4093,10 @@
         <v>76</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -4089,10 +4107,10 @@
         <v>77</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -4103,10 +4121,10 @@
         <v>78</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -4117,10 +4135,10 @@
         <v>79</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -4131,10 +4149,10 @@
         <v>80</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -4142,13 +4160,13 @@
         <v>315</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -4159,10 +4177,10 @@
         <v>81</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -4173,10 +4191,10 @@
         <v>82</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -4187,10 +4205,10 @@
         <v>83</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -4201,10 +4219,10 @@
         <v>84</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -4212,13 +4230,13 @@
         <v>325</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -4229,10 +4247,10 @@
         <v>85</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -4243,10 +4261,10 @@
         <v>86</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -4257,10 +4275,10 @@
         <v>87</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -4268,13 +4286,13 @@
         <v>346</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="D116" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="D116" s="8" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -4285,10 +4303,10 @@
         <v>88</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -4296,13 +4314,13 @@
         <v>358</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -4313,10 +4331,10 @@
         <v>89</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -4327,10 +4345,10 @@
         <v>90</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -4338,13 +4356,13 @@
         <v>364</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -4352,13 +4370,13 @@
         <v>366</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -4366,13 +4384,13 @@
         <v>372</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -4380,13 +4398,13 @@
         <v>375</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -4394,13 +4412,13 @@
         <v>379</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -4411,10 +4429,10 @@
         <v>91</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -4422,13 +4440,13 @@
         <v>383</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>92</v>
+        <v>686</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -4436,13 +4454,13 @@
         <v>385</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -4450,13 +4468,13 @@
         <v>393</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -4464,13 +4482,13 @@
         <v>394</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -4478,13 +4496,13 @@
         <v>395</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C131" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="D131" s="8" t="s">
         <v>604</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -4492,13 +4510,13 @@
         <v>398</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -4506,13 +4524,13 @@
         <v>400</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -4520,13 +4538,13 @@
         <v>401</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -4534,13 +4552,13 @@
         <v>408</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -4548,13 +4566,13 @@
         <v>413</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -4562,13 +4580,13 @@
         <v>415</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -4576,13 +4594,13 @@
         <v>417</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C138" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="D138" s="8" t="s">
         <v>609</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="D138" s="8" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -4590,13 +4608,13 @@
         <v>420</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H139" s="18"/>
     </row>
@@ -4605,13 +4623,13 @@
         <v>429</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -4619,13 +4637,13 @@
         <v>431</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -4633,13 +4651,13 @@
         <v>434</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -4647,13 +4665,13 @@
         <v>442</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -4661,13 +4679,13 @@
         <v>443</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4675,13 +4693,13 @@
         <v>445</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4689,13 +4707,13 @@
         <v>449</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4703,13 +4721,13 @@
         <v>456</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4717,13 +4735,13 @@
         <v>463</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4731,13 +4749,13 @@
         <v>471</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C149" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="D149" s="8" t="s">
         <v>621</v>
-      </c>
-      <c r="C149" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="D149" s="8" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4745,13 +4763,13 @@
         <v>473</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4759,13 +4777,13 @@
         <v>475</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4773,13 +4791,13 @@
         <v>476</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4787,13 +4805,13 @@
         <v>477</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4801,13 +4819,13 @@
         <v>481</v>
       </c>
       <c r="B154" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C154" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="D154" s="8" t="s">
         <v>613</v>
-      </c>
-      <c r="C154" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="D154" s="8" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4815,13 +4833,13 @@
         <v>485</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4829,13 +4847,13 @@
         <v>492</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -4843,13 +4861,13 @@
         <v>493</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4857,13 +4875,13 @@
         <v>499</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -4871,13 +4889,13 @@
         <v>502</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4885,13 +4903,13 @@
         <v>504</v>
       </c>
       <c r="B160" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="D160" s="8" t="s">
         <v>615</v>
-      </c>
-      <c r="C160" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="D160" s="8" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4899,13 +4917,13 @@
         <v>506</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -4913,13 +4931,13 @@
         <v>513</v>
       </c>
       <c r="B162" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C162" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="D162" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="C162" s="14" t="s">
-        <v>564</v>
-      </c>
-      <c r="D162" s="8" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4927,13 +4945,13 @@
         <v>515</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -4941,13 +4959,13 @@
         <v>517</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -4955,13 +4973,13 @@
         <v>523</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -4969,13 +4987,13 @@
         <v>528</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -4983,13 +5001,13 @@
         <v>536</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -4997,13 +5015,13 @@
         <v>539</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -5011,13 +5029,13 @@
         <v>544</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -5025,13 +5043,13 @@
         <v>554</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -5039,13 +5057,13 @@
         <v>560</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -5053,13 +5071,13 @@
         <v>566</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -5067,13 +5085,13 @@
         <v>573</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -5081,13 +5099,13 @@
         <v>580</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -5095,13 +5113,13 @@
         <v>582</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C175" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="D175" s="8" t="s">
         <v>619</v>
-      </c>
-      <c r="C175" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -5109,13 +5127,13 @@
         <v>586</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -5123,13 +5141,13 @@
         <v>589</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -5137,13 +5155,13 @@
         <v>591</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -5151,13 +5169,13 @@
         <v>592</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -5165,13 +5183,13 @@
         <v>593</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -5179,13 +5197,13 @@
         <v>594</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -5193,13 +5211,13 @@
         <v>595</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -5207,13 +5225,13 @@
         <v>604</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -5221,13 +5239,13 @@
         <v>605</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -5235,13 +5253,13 @@
         <v>610</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -5249,13 +5267,13 @@
         <v>611</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -5263,13 +5281,13 @@
         <v>613</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -5277,13 +5295,13 @@
         <v>614</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -5291,13 +5309,13 @@
         <v>618</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -5305,13 +5323,13 @@
         <v>619</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -5319,13 +5337,13 @@
         <v>626</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -5333,13 +5351,13 @@
         <v>628</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -5347,13 +5365,13 @@
         <v>629</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -5361,13 +5379,13 @@
         <v>631</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -5375,13 +5393,13 @@
         <v>635</v>
       </c>
       <c r="B195" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C195" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D195" s="8" t="s">
         <v>623</v>
-      </c>
-      <c r="C195" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="D195" s="8" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -5389,13 +5407,13 @@
         <v>636</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="C196" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D196" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="C196" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="D196" s="8" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -5403,13 +5421,13 @@
         <v>640</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -5417,13 +5435,13 @@
         <v>641</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C198" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D198" s="8" t="s">
         <v>628</v>
-      </c>
-      <c r="C198" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="D198" s="8" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -5431,13 +5449,13 @@
         <v>642</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C199" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="D199" s="8" t="s">
         <v>632</v>
-      </c>
-      <c r="C199" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="D199" s="8" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -5445,13 +5463,13 @@
         <v>647</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -5459,13 +5477,13 @@
         <v>653</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -5473,13 +5491,13 @@
         <v>654</v>
       </c>
       <c r="B202" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C202" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="D202" s="8" t="s">
         <v>630</v>
-      </c>
-      <c r="C202" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="D202" s="8" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -5487,13 +5505,13 @@
         <v>655</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C203" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -5501,13 +5519,13 @@
         <v>661</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5515,13 +5533,13 @@
         <v>662</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -5529,13 +5547,13 @@
         <v>668</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -5543,13 +5561,13 @@
         <v>675</v>
       </c>
       <c r="B207" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C207" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="D207" s="8" t="s">
         <v>664</v>
-      </c>
-      <c r="C207" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="D207" s="8" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -5557,13 +5575,13 @@
         <v>679</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -5571,13 +5589,13 @@
         <v>681</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -5585,13 +5603,13 @@
         <v>683</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -5599,13 +5617,13 @@
         <v>689</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -5613,13 +5631,13 @@
         <v>695</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5627,13 +5645,13 @@
         <v>698</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5641,13 +5659,13 @@
         <v>700</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5655,13 +5673,13 @@
         <v>701</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5669,13 +5687,13 @@
         <v>702</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5683,13 +5701,13 @@
         <v>703</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5697,13 +5715,13 @@
         <v>704</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5711,13 +5729,13 @@
         <v>706</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5725,13 +5743,13 @@
         <v>708</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5739,13 +5757,13 @@
         <v>710</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C221" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5753,13 +5771,13 @@
         <v>711</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5767,13 +5785,13 @@
         <v>713</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5781,13 +5799,13 @@
         <v>714</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5795,13 +5813,13 @@
         <v>715</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5809,13 +5827,13 @@
         <v>716</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5823,13 +5841,13 @@
         <v>717</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5837,13 +5855,13 @@
         <v>718</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C228" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5851,13 +5869,13 @@
         <v>720</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5865,13 +5883,13 @@
         <v>721</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5879,13 +5897,13 @@
         <v>722</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5893,13 +5911,13 @@
         <v>723</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C232" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5907,13 +5925,13 @@
         <v>724</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C233" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -5921,13 +5939,13 @@
         <v>731</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5938,10 +5956,10 @@
         <v>60</v>
       </c>
       <c r="C235" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D235" s="8" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -5949,13 +5967,13 @@
         <v>737</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C236" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -5963,13 +5981,13 @@
         <v>738</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C237" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5977,13 +5995,13 @@
         <v>745</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C238" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -5991,13 +6009,13 @@
         <v>746</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C239" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -6005,13 +6023,13 @@
         <v>747</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C240" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -6019,13 +6037,13 @@
         <v>748</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C241" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -6033,13 +6051,13 @@
         <v>750</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -6047,13 +6065,13 @@
         <v>754</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C243" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -6061,13 +6079,13 @@
         <v>755</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C244" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -6075,13 +6093,13 @@
         <v>756</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C245" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -6089,13 +6107,13 @@
         <v>759</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C246" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -6103,13 +6121,13 @@
         <v>762</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C247" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -6117,13 +6135,13 @@
         <v>763</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -6131,13 +6149,13 @@
         <v>767</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C249" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="D249" s="8" t="s">
         <v>668</v>
-      </c>
-      <c r="C249" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="D249" s="8" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -6145,13 +6163,13 @@
         <v>780</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -6159,13 +6177,13 @@
         <v>783</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C251" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -6173,13 +6191,13 @@
         <v>784</v>
       </c>
       <c r="B252" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="C252" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="D252" s="8" t="s">
         <v>670</v>
-      </c>
-      <c r="C252" s="11" t="s">
-        <v>547</v>
-      </c>
-      <c r="D252" s="8" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -6187,13 +6205,13 @@
         <v>787</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C253" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -6201,13 +6219,13 @@
         <v>791</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C254" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -6215,13 +6233,13 @@
         <v>792</v>
       </c>
       <c r="B255" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C255" s="11" t="s">
         <v>672</v>
       </c>
-      <c r="C255" s="11" t="s">
+      <c r="D255" s="8" t="s">
         <v>673</v>
-      </c>
-      <c r="D255" s="8" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -6229,13 +6247,13 @@
         <v>793</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C256" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -6243,13 +6261,13 @@
         <v>797</v>
       </c>
       <c r="B257" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="D257" s="8" t="s">
         <v>666</v>
-      </c>
-      <c r="C257" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="D257" s="8" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -6257,13 +6275,13 @@
         <v>799</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -6271,13 +6289,13 @@
         <v>801</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C259" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -6285,13 +6303,13 @@
         <v>805</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -6299,13 +6317,13 @@
         <v>807</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C261" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -6313,13 +6331,13 @@
         <v>809</v>
       </c>
       <c r="B262" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C262" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="D262" s="8" t="s">
         <v>675</v>
-      </c>
-      <c r="C262" s="11" t="s">
-        <v>673</v>
-      </c>
-      <c r="D262" s="8" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -6327,13 +6345,13 @@
         <v>810</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C263" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -6341,13 +6359,13 @@
         <v>811</v>
       </c>
       <c r="B264" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C264" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="D264" s="8" t="s">
         <v>677</v>
-      </c>
-      <c r="C264" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="D264" s="8" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -6355,13 +6373,13 @@
         <v>812</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C265" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -6369,13 +6387,13 @@
         <v>815</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -6383,13 +6401,13 @@
         <v>818</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C267" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6397,13 +6415,13 @@
         <v>819</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6411,13 +6429,13 @@
         <v>821</v>
       </c>
       <c r="B269" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="D269" s="8" t="s">
         <v>679</v>
-      </c>
-      <c r="C269" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="D269" s="8" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6425,13 +6443,13 @@
         <v>824</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D270" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -6439,13 +6457,13 @@
         <v>826</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C271" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -6453,13 +6471,13 @@
         <v>828</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C272" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6467,909 +6485,951 @@
         <v>830</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="20">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>658</v>
+        <v>680</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>276</v>
+        <v>681</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="20">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C275" s="9" t="s">
-        <v>547</v>
+        <v>657</v>
+      </c>
+      <c r="C275" s="12" t="s">
+        <v>559</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="20">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C276" s="9" t="s">
-        <v>547</v>
+        <v>682</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>546</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>278</v>
+        <v>683</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="20">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C277" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="20">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="20">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C279" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="20">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="20">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C281" s="9" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="D281" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="20">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C282" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="20">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>659</v>
+        <v>201</v>
       </c>
       <c r="C283" s="9" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="20">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C284" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D284" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="20">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>205</v>
+        <v>658</v>
       </c>
       <c r="C285" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D285" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="20">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>660</v>
+        <v>203</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D286" s="8" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="20">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C287" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="20">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>207</v>
+        <v>659</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D288" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="20">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C289" s="11" t="s">
-        <v>547</v>
+        <v>205</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="20">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C290" s="9" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="D290" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="20">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C291" s="9" t="s">
-        <v>547</v>
+        <v>207</v>
+      </c>
+      <c r="C291" s="11" t="s">
+        <v>546</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="20">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C292" s="12" t="s">
-        <v>560</v>
+        <v>684</v>
+      </c>
+      <c r="C292" s="11" t="s">
+        <v>546</v>
       </c>
       <c r="D292" s="8" t="s">
-        <v>294</v>
+        <v>685</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="20">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C293" s="12" t="s">
-        <v>560</v>
+        <v>208</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>563</v>
       </c>
       <c r="D293" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="20">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D294" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="20">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C295" s="9" t="s">
-        <v>564</v>
+        <v>210</v>
+      </c>
+      <c r="C295" s="12" t="s">
+        <v>559</v>
       </c>
       <c r="D295" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="20">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C296" s="9" t="s">
-        <v>564</v>
+        <v>211</v>
+      </c>
+      <c r="C296" s="12" t="s">
+        <v>559</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="20">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C297" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D297" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="20">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="D298" s="8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="20">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="D299" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="20">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="20">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C301" s="12" t="s">
-        <v>560</v>
+        <v>216</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="D301" s="8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="20">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C302" s="11" t="s">
-        <v>547</v>
+        <v>217</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>546</v>
       </c>
       <c r="D302" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="20">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C303" s="9" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="D303" s="8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="20">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C304" s="9" t="s">
-        <v>549</v>
+        <v>219</v>
+      </c>
+      <c r="C304" s="12" t="s">
+        <v>559</v>
       </c>
       <c r="D304" s="8" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="20">
-        <v>902</v>
+        <v>892</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C305" s="9" t="s">
-        <v>547</v>
+        <v>220</v>
+      </c>
+      <c r="C305" s="11" t="s">
+        <v>546</v>
       </c>
       <c r="D305" s="8" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="20">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="D306" s="8" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="20">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D307" s="8" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="20">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D308" s="8" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="20">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C309" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D309" s="8" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="20">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C310" s="9" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="D310" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="20">
-        <v>926</v>
+        <v>911</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C311" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D311" s="8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="20">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C312" s="12" t="s">
-        <v>560</v>
+        <v>227</v>
+      </c>
+      <c r="C312" s="9" t="s">
+        <v>546</v>
       </c>
       <c r="D312" s="8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="20">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C313" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D313" s="8" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="20">
-        <v>938</v>
+        <v>926</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D314" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="20">
-        <v>942</v>
+        <v>927</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="C315" s="9" t="s">
-        <v>563</v>
+        <v>230</v>
+      </c>
+      <c r="C315" s="12" t="s">
+        <v>559</v>
       </c>
       <c r="D315" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="20">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="D316" s="8" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="20">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>635</v>
+        <v>232</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D317" s="8" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="20">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>234</v>
+        <v>633</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="20">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D319" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="20">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>236</v>
+        <v>634</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="D320" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="20">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D321" s="8" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="20">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C322" s="15" t="s">
-        <v>547</v>
+        <v>234</v>
+      </c>
+      <c r="C322" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="D322" s="8" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="20">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C323" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="D323" s="13" t="s">
-        <v>325</v>
+        <v>563</v>
+      </c>
+      <c r="D323" s="8" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="20">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C324" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="D324" s="13" t="s">
-        <v>326</v>
+        <v>546</v>
+      </c>
+      <c r="D324" s="8" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="20">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="C325" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="D325" s="13" t="s">
-        <v>327</v>
+        <v>237</v>
+      </c>
+      <c r="C325" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="D325" s="8" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="20">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C326" s="16" t="s">
-        <v>547</v>
+        <v>238</v>
+      </c>
+      <c r="C326" s="9" t="s">
+        <v>546</v>
       </c>
       <c r="D326" s="13" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="20">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="C327" s="16" t="s">
-        <v>564</v>
+        <v>239</v>
+      </c>
+      <c r="C327" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="D327" s="13" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="20">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>241</v>
+        <v>660</v>
       </c>
       <c r="C328" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D328" s="13" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="20">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C329" s="9" t="s">
-        <v>547</v>
+        <v>661</v>
+      </c>
+      <c r="C329" s="16" t="s">
+        <v>546</v>
       </c>
       <c r="D329" s="13" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="20">
-        <v>983</v>
+        <v>968</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C330" s="9" t="s">
-        <v>549</v>
+        <v>662</v>
+      </c>
+      <c r="C330" s="16" t="s">
+        <v>563</v>
       </c>
       <c r="D330" s="13" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="20">
-        <v>985</v>
+        <v>972</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C331" s="16" t="s">
-        <v>549</v>
+        <v>240</v>
+      </c>
+      <c r="C331" s="9" t="s">
+        <v>546</v>
       </c>
       <c r="D331" s="13" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="20">
-        <v>989</v>
+        <v>975</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C332" s="9" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="D332" s="13" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="20">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C333" s="19" t="s">
-        <v>560</v>
+        <v>242</v>
+      </c>
+      <c r="C333" s="9" t="s">
+        <v>548</v>
       </c>
       <c r="D333" s="13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="20">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C334" s="9" t="s">
-        <v>549</v>
+        <v>243</v>
+      </c>
+      <c r="C334" s="16" t="s">
+        <v>548</v>
       </c>
       <c r="D334" s="13" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="20">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C335" s="16" t="s">
-        <v>549</v>
+        <v>244</v>
+      </c>
+      <c r="C335" s="9" t="s">
+        <v>563</v>
       </c>
       <c r="D335" s="13" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="20">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C336" s="16" t="s">
-        <v>547</v>
+        <v>245</v>
+      </c>
+      <c r="C336" s="19" t="s">
+        <v>559</v>
       </c>
       <c r="D336" s="13" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="20">
+        <v>991</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C337" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="D337" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="20">
+        <v>996</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C338" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="D338" s="13" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="20">
+        <v>998</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C339" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D339" s="13" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="20">
         <v>4006</v>
       </c>
-      <c r="B337" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C337" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="D337" s="13" t="s">
-        <v>546</v>
+      <c r="B340" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C340" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="D340" s="13" t="s">
+        <v>545</v>
       </c>
     </row>
   </sheetData>

--- a/BASE/DADOS_CONDOMINIOS.xlsx
+++ b/BASE/DADOS_CONDOMINIOS.xlsx
@@ -5,2098 +5,2073 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Wallpaper\NF GW\NF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.moreira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F6BDE2-70B2-40FB-A631-D069774A69CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5124F5F7-7C6B-4600-BFAC-C327FACB504E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{06283720-90B9-47BF-AEF6-ACB6BB5B8FC8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COND" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="684">
+  <si>
+    <t>COD</t>
+  </si>
+  <si>
+    <t>CONDOMINIO</t>
+  </si>
+  <si>
+    <t>GESTAO</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
+  </si>
   <si>
     <t xml:space="preserve">MODESTO STARLING </t>
   </si>
   <si>
+    <t>PLUS</t>
+  </si>
+  <si>
+    <t>19.270.149/0001-19</t>
+  </si>
+  <si>
+    <t>SAO CARLOS</t>
+  </si>
+  <si>
+    <t>PLUS-SIC</t>
+  </si>
+  <si>
+    <t>38.419.086/0001-64</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANA PAULA </t>
   </si>
   <si>
+    <t>FOLHA</t>
+  </si>
+  <si>
+    <t>26.388.793/0001-51</t>
+  </si>
+  <si>
     <t>CORNELIO LIMA RODRIGUES</t>
   </si>
   <si>
+    <t>26.232.066/0001-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARQUE SAO BENTO </t>
   </si>
   <si>
+    <t>C_EMITE</t>
+  </si>
+  <si>
+    <t>25.530.528/0001-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONTECHIARO </t>
   </si>
   <si>
+    <t>GESTORA</t>
+  </si>
+  <si>
+    <t>65.148.751/0001-03</t>
+  </si>
+  <si>
+    <t>RESIDENCIAL LIMA ROSA</t>
+  </si>
+  <si>
+    <t>34.504.252/0001-70</t>
+  </si>
+  <si>
+    <t>MARYSE</t>
+  </si>
+  <si>
+    <t>20.185.989/0001-62</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL CHAVES CANCADO</t>
+  </si>
+  <si>
+    <t>23.168.225/0001-57</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONTE CARLO </t>
   </si>
   <si>
+    <t>65.143.075/0001-77</t>
+  </si>
+  <si>
     <t xml:space="preserve">VILA MARIANA </t>
   </si>
   <si>
+    <t>42.788.919/0001-31</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARVALHO DE BRITO </t>
   </si>
   <si>
+    <t>20.473.187/0001-58</t>
+  </si>
+  <si>
     <t>SAO GERALDO</t>
   </si>
   <si>
+    <t>25.468.778/0001-50</t>
+  </si>
+  <si>
     <t>SINDICON</t>
   </si>
   <si>
+    <t>CHEQUE</t>
+  </si>
+  <si>
+    <t>25.568.882/0001-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">DANIEL </t>
   </si>
   <si>
+    <t>02.173.659/0001-75</t>
+  </si>
+  <si>
+    <t>CASABLANCA</t>
+  </si>
+  <si>
+    <t>10.771.643/0001-92</t>
+  </si>
+  <si>
     <t>CONTORNO PLAZA</t>
   </si>
   <si>
+    <t>38.741.526/0001-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONTE BRANCO </t>
   </si>
   <si>
+    <t>42.778.878/0001-00</t>
+  </si>
+  <si>
+    <t>DIAMANTE</t>
+  </si>
+  <si>
+    <t>04.100.983/0001-99</t>
+  </si>
+  <si>
     <t xml:space="preserve">GIOVANNA </t>
   </si>
   <si>
+    <t>00.494.979/0001-00</t>
+  </si>
+  <si>
     <t xml:space="preserve">FERNANDO DANTAS </t>
   </si>
   <si>
+    <t>42.779.744/0001-04</t>
+  </si>
+  <si>
     <t>NOSSA SENHORA DA GUIA</t>
   </si>
   <si>
+    <t>86.839.859/0001-04</t>
+  </si>
+  <si>
     <t>PIATAN</t>
   </si>
   <si>
+    <t>42.764.399/0001-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">VALENCIA </t>
   </si>
   <si>
+    <t>12.513.839/0001-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRONZI DE RIACI </t>
   </si>
   <si>
+    <t>03.023.476/0001-36</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRITANIA </t>
   </si>
   <si>
+    <t>65.158.586/0001-62</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMELIA FRANCO </t>
   </si>
   <si>
+    <t>00.740.218/0001-82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM CABRAL </t>
+  </si>
+  <si>
+    <t>00.906.063/0001-01</t>
+  </si>
+  <si>
+    <t>CAMILA CAETANO</t>
+  </si>
+  <si>
+    <t>02.651.835/0001-37</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAVID BORJA </t>
   </si>
   <si>
+    <t>26.385.054/0001-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">TORRE LA DEFENSE </t>
   </si>
   <si>
+    <t>01.335.765/0001-45</t>
+  </si>
+  <si>
     <t xml:space="preserve">AGATA </t>
   </si>
   <si>
+    <t>00.931.382/0001-77</t>
+  </si>
+  <si>
     <t>DOM LUIZ I</t>
   </si>
   <si>
+    <t>01.774.760/0001-19</t>
+  </si>
+  <si>
     <t>NOSSA SENHORA DE FATIMA</t>
   </si>
   <si>
+    <t>03.606.174/0001-90</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRESIDENTE </t>
   </si>
   <si>
+    <t>42.765.362/0001-13</t>
+  </si>
+  <si>
     <t>TURMALINA</t>
   </si>
   <si>
+    <t>09.069.496/0001-24</t>
+  </si>
+  <si>
     <t>AMADEUS MOZART</t>
   </si>
   <si>
+    <t>11.177.026/0001-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">ABROLHOS </t>
   </si>
   <si>
+    <t>00.697.217/0001-00</t>
+  </si>
+  <si>
+    <t>AZURITA</t>
+  </si>
+  <si>
+    <t>05.217.866/0001-72</t>
+  </si>
+  <si>
     <t xml:space="preserve">VILA PARIS </t>
   </si>
   <si>
+    <t>PLUS-CEF</t>
+  </si>
+  <si>
+    <t>00.639.590/0001-05</t>
+  </si>
+  <si>
     <t xml:space="preserve">SOBERANO </t>
   </si>
   <si>
+    <t>70.953.575/0001-04</t>
+  </si>
+  <si>
     <t>NINI</t>
   </si>
   <si>
+    <t>20.999.819/0001-11</t>
+  </si>
+  <si>
     <t>MALAGA</t>
   </si>
   <si>
+    <t>42.763.722/0001-48</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARCELO COSTA </t>
   </si>
   <si>
+    <t>70.956.867/0001-09</t>
+  </si>
+  <si>
     <t>OLIMPUS</t>
   </si>
   <si>
+    <t>65.170.763/0001-26</t>
+  </si>
+  <si>
     <t>RAISSA</t>
   </si>
   <si>
+    <t>07.235.068/0001-07</t>
+  </si>
+  <si>
     <t>PLACE VERSALHES</t>
   </si>
   <si>
+    <t>PLUS-PJ</t>
+  </si>
+  <si>
+    <t>40.484.041/0001-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARISTEU MUSCHIONI </t>
+  </si>
+  <si>
+    <t>00.116.412/0001-91</t>
+  </si>
+  <si>
     <t xml:space="preserve">LYANE BALDAN </t>
   </si>
   <si>
+    <t>01.971.539/0001-50</t>
+  </si>
+  <si>
     <t xml:space="preserve">HIBISCO </t>
   </si>
   <si>
+    <t>03.058.185/0001-83</t>
+  </si>
+  <si>
     <t xml:space="preserve">CANOPUS </t>
   </si>
   <si>
+    <t>03.245.064/0001-40</t>
+  </si>
+  <si>
     <t>FILIPPO BRUNNELLESCHE</t>
   </si>
   <si>
+    <t>02.291.972/0001-08</t>
+  </si>
+  <si>
+    <t>PALMARES</t>
+  </si>
+  <si>
+    <t>29.457.416/0001-15</t>
+  </si>
+  <si>
+    <t>PALAIS DE VERSAILLES</t>
+  </si>
+  <si>
+    <t>20.461.885/0001-33</t>
+  </si>
+  <si>
     <t xml:space="preserve">UBATUBA </t>
   </si>
   <si>
+    <t>02.712.276/0001-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">MALIBU </t>
   </si>
   <si>
+    <t>65.162.430/0001-55</t>
+  </si>
+  <si>
     <t>VILA DEL REY</t>
   </si>
   <si>
+    <t>00.143.954/0001-53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUADALUPE </t>
+  </si>
+  <si>
+    <t>42.767.475/0001-58</t>
+  </si>
+  <si>
     <t>BEETHOVEN</t>
   </si>
   <si>
+    <t>03.558.818/0001-12</t>
+  </si>
+  <si>
     <t>SOLAR DOS PINHEIROS</t>
   </si>
   <si>
+    <t>65.177.339/0001-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">INCONFIDENTES </t>
   </si>
   <si>
+    <t>20.473.161/0001-00</t>
+  </si>
+  <si>
     <t xml:space="preserve">ELIANA </t>
   </si>
   <si>
+    <t>97.491.260/0001-49</t>
+  </si>
+  <si>
+    <t>JOSE MARTINS DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>03.069.991/0001-57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAMOND ARCH </t>
+  </si>
+  <si>
+    <t>02.028.860/0001-69</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARK SATURNO </t>
   </si>
   <si>
+    <t>34.429.769/0001-41</t>
+  </si>
+  <si>
     <t>DEBORAH</t>
   </si>
   <si>
+    <t>42.771.766/0001-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">RIO VERDE </t>
   </si>
   <si>
+    <t>21.507.371/0001-34</t>
+  </si>
+  <si>
     <t xml:space="preserve">KALIL FARID </t>
   </si>
   <si>
+    <t>11.867.583/0001-79</t>
+  </si>
+  <si>
     <t xml:space="preserve">PALO ALTO </t>
   </si>
   <si>
+    <t>04.338.277/0001-80</t>
+  </si>
+  <si>
     <t>ROBERVAL</t>
   </si>
   <si>
+    <t>03.085.700/0001-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">GAUDI </t>
   </si>
   <si>
+    <t>97.424.295/0001-65</t>
+  </si>
+  <si>
     <t>VENEZA</t>
   </si>
   <si>
+    <t>00.098.286/0001-90</t>
+  </si>
+  <si>
     <t>LUCY</t>
   </si>
   <si>
+    <t>24.025.801/0001-70</t>
+  </si>
+  <si>
     <t xml:space="preserve">JOAO VIANA </t>
   </si>
   <si>
+    <t>73.878.951/0001-31</t>
+  </si>
+  <si>
+    <t>MARIA LUIZA</t>
+  </si>
+  <si>
+    <t>04.904.825/0001-91</t>
+  </si>
+  <si>
     <t xml:space="preserve">TRINITA </t>
   </si>
   <si>
+    <t>08.041.935/0001-28</t>
+  </si>
+  <si>
     <t>BELMONTE</t>
   </si>
   <si>
+    <t>00.708.692/0001-27</t>
+  </si>
+  <si>
     <t>RIYADH</t>
   </si>
   <si>
+    <t>33.497.533/0001-80</t>
+  </si>
+  <si>
     <t>FIRENZE</t>
   </si>
   <si>
+    <t>10.966.799/0001-29</t>
+  </si>
+  <si>
     <t>TININHO BORGES</t>
   </si>
   <si>
+    <t>25.572.470/0001-50</t>
+  </si>
+  <si>
+    <t>DOM LUCCILIO</t>
+  </si>
+  <si>
+    <t>00.568.356/0001-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAN REMO </t>
   </si>
   <si>
+    <t>02.312.855/0001-83</t>
+  </si>
+  <si>
+    <t>ANITA CIOLETTI</t>
+  </si>
+  <si>
+    <t>01.383.665/0001-94</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>56.226.238/0001-94</t>
+  </si>
+  <si>
     <t>CICERO RIOS</t>
   </si>
   <si>
+    <t>25.455.262/0001-71</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
+  </si>
+  <si>
+    <t>57.490.281/0001-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">GUIMARAES PENA </t>
   </si>
   <si>
+    <t>04.114.656/0001-96</t>
+  </si>
+  <si>
     <t xml:space="preserve">VIVARINI </t>
   </si>
   <si>
+    <t>04.247.555/0001-93</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONTE DOR </t>
   </si>
   <si>
+    <t>16.842.756/0001-18</t>
+  </si>
+  <si>
+    <t>IPE</t>
+  </si>
+  <si>
+    <t>23.971.443/0001-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">BANDEIRANTES </t>
   </si>
   <si>
+    <t>01.067.088/0001-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">PARQUE BELVEDERE </t>
   </si>
   <si>
+    <t>04.275.179/0001-40</t>
+  </si>
+  <si>
+    <t>PAULO EDUARDO</t>
+  </si>
+  <si>
+    <t>38.727.624/0001-88</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRASIL RESIDENCE </t>
   </si>
   <si>
+    <t>42.784.769/0001-98</t>
+  </si>
+  <si>
     <t xml:space="preserve">IATROS </t>
   </si>
   <si>
+    <t>65.145.518/0001-69</t>
+  </si>
+  <si>
     <t>CEGEDE II</t>
   </si>
   <si>
+    <t>02.202.492/0001-23</t>
+  </si>
+  <si>
+    <t>LA CORUNA</t>
+  </si>
+  <si>
+    <t>04.558.217/0001-72</t>
+  </si>
+  <si>
     <t>DURVAL GROSSI</t>
   </si>
   <si>
+    <t>05.080.984/0001-81</t>
+  </si>
+  <si>
+    <t>MARCIA HELENA</t>
+  </si>
+  <si>
+    <t>48.922.623/0001-48</t>
+  </si>
+  <si>
     <t xml:space="preserve">IGNACIA CARDOSO </t>
   </si>
   <si>
+    <t>70.946.108/0001-57</t>
+  </si>
+  <si>
     <t>NOSSA SRA DIVINA PROVIDENCIA</t>
   </si>
   <si>
+    <t>07.135.705/0001-65</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUMA </t>
   </si>
   <si>
+    <t>65.156.861/0001-09</t>
+  </si>
+  <si>
     <t>TRIUNPHO</t>
   </si>
   <si>
+    <t>01.482.514/0001-93</t>
+  </si>
+  <si>
     <t xml:space="preserve">COSTA BELLA </t>
   </si>
   <si>
+    <t>05.085.456/0001-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">DOM PAOLO </t>
   </si>
   <si>
+    <t>65.181.638/0001-11</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>42.781.542/0001-99</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARIO FERRARI </t>
   </si>
   <si>
+    <t>01.806.572/0001-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">VILLE DE FRANCE </t>
   </si>
   <si>
+    <t>23.217.664/0001-02</t>
+  </si>
+  <si>
     <t>VALLE D'AMPEZZO</t>
   </si>
   <si>
+    <t>05.082.435/0001-46</t>
+  </si>
+  <si>
     <t xml:space="preserve">BERENICE </t>
   </si>
   <si>
+    <t>01.195.567/0001-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUTHER KING </t>
+  </si>
+  <si>
+    <t>04.870.726/0001-36</t>
+  </si>
+  <si>
     <t>CECI</t>
   </si>
   <si>
+    <t>00.867.641/0001-48</t>
+  </si>
+  <si>
     <t>PALMEIRAS</t>
   </si>
   <si>
+    <t>74.148.420/0001-56</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALMEIDA CAMPOS </t>
   </si>
   <si>
+    <t>65.152.126/0001-27</t>
+  </si>
+  <si>
+    <t>ANTONIO MOURA</t>
+  </si>
+  <si>
+    <t>15.045.757/0001-79</t>
+  </si>
+  <si>
     <t>NANDIA</t>
   </si>
   <si>
+    <t>02.232.226/0001-43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINHO M MENDONCA </t>
+  </si>
+  <si>
+    <t>25.704.115/0001-98</t>
+  </si>
+  <si>
     <t>DJALMA PASSOS VELOSO</t>
   </si>
   <si>
+    <t>08.811.255/0001-46</t>
+  </si>
+  <si>
     <t xml:space="preserve">VERONA </t>
   </si>
   <si>
+    <t>05.629.236/0001-05</t>
+  </si>
+  <si>
+    <t>CAMPOS ELISEOS</t>
+  </si>
+  <si>
+    <t>26.231.985/0001-50</t>
+  </si>
+  <si>
+    <t>ELPIDIO CORDEIRO DO COUTO</t>
+  </si>
+  <si>
+    <t>42.772.103/0001-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRES DO HORIZONTE </t>
+  </si>
+  <si>
+    <t>44.594.887/0001-69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAINT GERMAIN </t>
+  </si>
+  <si>
+    <t>03.150.555/0001-08</t>
+  </si>
+  <si>
+    <t>MARCOLLA</t>
+  </si>
+  <si>
+    <t>26.231.019/0001-32</t>
+  </si>
+  <si>
     <t xml:space="preserve">SENHOR DO BONFIM </t>
   </si>
   <si>
+    <t>07.572.539/0001-64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN ROMAN </t>
+  </si>
+  <si>
+    <t>06.049.617/0001-88</t>
+  </si>
+  <si>
     <t>ARTHUR AUGUSTO</t>
   </si>
   <si>
+    <t>74.053.810/0001-42</t>
+  </si>
+  <si>
     <t xml:space="preserve">RIVIERA </t>
   </si>
   <si>
+    <t>71.089.122/0001-44</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONICA </t>
   </si>
   <si>
+    <t>04.398.998/0001-85</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>70.955.836/0001-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">BARCELONA </t>
   </si>
   <si>
+    <t>86.692.787/0001-15</t>
+  </si>
+  <si>
     <t>5ª AVENIDA</t>
   </si>
   <si>
+    <t>20.446.647/0001-59</t>
+  </si>
+  <si>
+    <t>JOAO LUIZ DE FREITAS</t>
+  </si>
+  <si>
+    <t>06.375.532/0001-90</t>
+  </si>
+  <si>
     <t xml:space="preserve">TECH TOWER </t>
   </si>
   <si>
+    <t>00.639.593/0001-30</t>
+  </si>
+  <si>
+    <t>RAJA PLUS</t>
+  </si>
+  <si>
+    <t>13.471.226/0001-12</t>
+  </si>
+  <si>
     <t>NOTRE DAME</t>
   </si>
   <si>
+    <t>02.229.281/0001-84</t>
+  </si>
+  <si>
+    <t>RESERVA LAGUNA</t>
+  </si>
+  <si>
+    <t>55.066.652/0001-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">GUIANAS </t>
   </si>
   <si>
+    <t>02.701.075/0001-25</t>
+  </si>
+  <si>
     <t>RURAL RECANTO DA SERRA</t>
   </si>
   <si>
+    <t>04.170.257/0001-42</t>
+  </si>
+  <si>
+    <t>EVERARDO VIEIRA</t>
+  </si>
+  <si>
+    <t>42.765.305/0001-34</t>
+  </si>
+  <si>
     <t>IRENE VIEITAS FABRINI</t>
   </si>
   <si>
+    <t>05.350.922/0001-42</t>
+  </si>
+  <si>
     <t xml:space="preserve">EILAT </t>
   </si>
   <si>
+    <t>29.536.510/0001-60</t>
+  </si>
+  <si>
     <t xml:space="preserve">VILA MARINHOS </t>
   </si>
   <si>
+    <t>00.479.772/0001-58</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARISE </t>
   </si>
   <si>
+    <t>65.180.440/0001-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">RIVADAVIA MOREIRA </t>
   </si>
   <si>
+    <t>40.119.057/0001-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTO BELLO </t>
+  </si>
+  <si>
+    <t>25.695.040/0001-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">BOM TEMPO </t>
   </si>
   <si>
+    <t>65.164.857/0001-92</t>
+  </si>
+  <si>
+    <t>RESERVA DAS PALMEIRAS</t>
+  </si>
+  <si>
+    <t>60.521.832/0001-85</t>
+  </si>
+  <si>
     <t xml:space="preserve">HARVARD </t>
   </si>
   <si>
+    <t>05.230.129/0001-00</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANA LUCIA </t>
   </si>
   <si>
+    <t>26.387.464/0001-96</t>
+  </si>
+  <si>
+    <t>ANTONIO DE CASTRO</t>
+  </si>
+  <si>
+    <t>25.693.474/0001-97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILLE FRANCHE </t>
+  </si>
+  <si>
+    <t>01.118.248/0001-14</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>73.516.023/0001-27</t>
+  </si>
+  <si>
     <t xml:space="preserve">LEANE </t>
   </si>
   <si>
+    <t>08.109.602/0001-93</t>
+  </si>
+  <si>
     <t>FLICKA</t>
   </si>
   <si>
+    <t>00.327.946/0001-67</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI RIVELO </t>
   </si>
   <si>
+    <t>07.547.257/0001-07</t>
+  </si>
+  <si>
     <t>DANTON</t>
   </si>
   <si>
+    <t>74.119.892/0001-80</t>
+  </si>
+  <si>
     <t xml:space="preserve">JUIZ DE FORA </t>
   </si>
   <si>
+    <t>19.792.399/0001-19</t>
+  </si>
+  <si>
+    <t>DIOGO VASCONCELOS</t>
+  </si>
+  <si>
+    <t>65.167.967/0001-08</t>
+  </si>
+  <si>
     <t>MONTE CASTELO</t>
   </si>
   <si>
+    <t>00.745.384/0001-71</t>
+  </si>
+  <si>
+    <t>INTERPARK</t>
+  </si>
+  <si>
+    <t>01.201.299/0001-05</t>
+  </si>
+  <si>
     <t xml:space="preserve">VIENA </t>
   </si>
   <si>
+    <t>01.564.428/0001-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">SONIA MARIA </t>
   </si>
   <si>
+    <t>00.177.244/0001-44</t>
+  </si>
+  <si>
     <t xml:space="preserve">BUGANVILA </t>
   </si>
   <si>
+    <t>01.502.972/0001-47</t>
+  </si>
+  <si>
     <t xml:space="preserve">QUELUZ </t>
   </si>
   <si>
+    <t>42.786.970/0001-04</t>
+  </si>
+  <si>
     <t>CANAAN</t>
   </si>
   <si>
+    <t>70.954.375/0001-76</t>
+  </si>
+  <si>
     <t>GISELE</t>
   </si>
   <si>
+    <t>02.940.446/0001-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAN MARINO </t>
   </si>
   <si>
+    <t>02.243.971/0001-98</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAX LINDER </t>
   </si>
   <si>
+    <t>02.972.746/0001-92</t>
+  </si>
+  <si>
     <t>RESIDENCIAL BARCELONA</t>
   </si>
   <si>
+    <t>65.144.800/0001-21</t>
+  </si>
+  <si>
     <t>BAETA VIANNA</t>
   </si>
   <si>
+    <t>70.942.610/0001-90</t>
+  </si>
+  <si>
     <t xml:space="preserve">FLORESTA GARDEN PARK </t>
   </si>
   <si>
+    <t>73.314.163/0001-12</t>
+  </si>
+  <si>
+    <t>DR. HELADIO J MARTINS</t>
+  </si>
+  <si>
+    <t>38.739.330/0001-76</t>
+  </si>
+  <si>
+    <t>CACUERA</t>
+  </si>
+  <si>
+    <t>60.620.800/0001-37</t>
+  </si>
+  <si>
     <t xml:space="preserve">JOSE ALVES REZENDE </t>
   </si>
   <si>
+    <t>00.745.388/0001-50</t>
+  </si>
+  <si>
+    <t>PORTA D'ORO</t>
+  </si>
+  <si>
+    <t>01.656.186/0001-02</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
+    <t>36.669.550/0001-45</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAINT FLORENT </t>
   </si>
   <si>
+    <t>11.808.031/0001-90</t>
+  </si>
+  <si>
+    <t>SAINT HONORE</t>
+  </si>
+  <si>
+    <t>00.434.396/0001-85</t>
+  </si>
+  <si>
     <t>COPENHAGEN</t>
   </si>
   <si>
+    <t>10.949.264/0001-40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAUL CEZZANNE </t>
+  </si>
+  <si>
+    <t>08.935.490/0001-20</t>
+  </si>
+  <si>
     <t>CHRISTIANE</t>
   </si>
   <si>
+    <t>12.482.928/0001-39</t>
+  </si>
+  <si>
     <t>DALLAS BUSINESS CENTER</t>
   </si>
   <si>
+    <t>00.385.739/0001-69</t>
+  </si>
+  <si>
     <t>ANTONIO GUIMARAES</t>
   </si>
   <si>
+    <t>01.906.498/0001-19</t>
+  </si>
+  <si>
     <t>PORTO SEGURO</t>
   </si>
   <si>
+    <t>03.077.558/0001-63</t>
+  </si>
+  <si>
     <t xml:space="preserve">SANTA CRUZ </t>
   </si>
   <si>
+    <t>70.951.181/0001-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOLPI SION </t>
+  </si>
+  <si>
+    <t>08.951.158/0001-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RACHEL COHEN </t>
+  </si>
+  <si>
+    <t>10.372.475/0001-62</t>
+  </si>
+  <si>
     <t>CONCORDE</t>
   </si>
   <si>
+    <t>65.150.773/0001-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONTEBIANCO </t>
   </si>
   <si>
+    <t>02.798.012/0001-39</t>
+  </si>
+  <si>
     <t>WILMA FIGUEIREDO BRANDT</t>
   </si>
   <si>
+    <t>04.479.304/0001-34</t>
+  </si>
+  <si>
     <t xml:space="preserve">FLORALIA </t>
   </si>
   <si>
+    <t>12.641.671/0001-10</t>
+  </si>
+  <si>
+    <t>TERESINHA BRANDAO RESENDE</t>
+  </si>
+  <si>
+    <t>12.126.907/0001-80</t>
+  </si>
+  <si>
+    <t>ALTHA DORTMUND</t>
+  </si>
+  <si>
+    <t>30.708.225/0001-68</t>
+  </si>
+  <si>
+    <t>SAN PELINO</t>
+  </si>
+  <si>
+    <t>02.693.218/0001-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">ADYNAN MARQUES </t>
   </si>
   <si>
+    <t>12.258.948/0001-20</t>
+  </si>
+  <si>
+    <t>SERRA DOS PINHAIS</t>
+  </si>
+  <si>
+    <t>52.081.752/0001-28</t>
+  </si>
+  <si>
+    <t>AGUAS CLARAS</t>
+  </si>
+  <si>
+    <t>42.775.312/0001-17</t>
+  </si>
+  <si>
+    <t>BUGANVILLE</t>
+  </si>
+  <si>
+    <t>26.229.724/0001-03</t>
+  </si>
+  <si>
     <t>SAN DIEGO</t>
   </si>
   <si>
+    <t>05.738.382/0001-79</t>
+  </si>
+  <si>
+    <t>JONAS BELIZARIO</t>
+  </si>
+  <si>
+    <t>26.269.738/0001-42</t>
+  </si>
+  <si>
     <t>VOLPI</t>
   </si>
   <si>
+    <t>13.299.611/0001-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRUNO CARLO </t>
   </si>
   <si>
+    <t>25.568.528/0001-92</t>
+  </si>
+  <si>
     <t>SEIS MARIAS</t>
   </si>
   <si>
+    <t>65.151.862/0001-60</t>
+  </si>
+  <si>
     <t>FLORENCE</t>
   </si>
   <si>
+    <t>26.388.969/0001-75</t>
+  </si>
+  <si>
+    <t>ASS. AlPHAVILLE LAGOA DOS INGLESES</t>
+  </si>
+  <si>
+    <t>03.826.434/0001-33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIWAN </t>
+  </si>
+  <si>
+    <t>65.148.728/0001-00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOWN HOUSE </t>
+  </si>
+  <si>
+    <t>04.815.709/0001-04</t>
+  </si>
+  <si>
     <t>ANDORINHA</t>
   </si>
   <si>
+    <t>05.241.115/0001-91</t>
+  </si>
+  <si>
     <t xml:space="preserve">NAPOLE </t>
   </si>
   <si>
+    <t>74.025.792/0001-95</t>
+  </si>
+  <si>
+    <t>ANTONIO PEDRO MACIEL</t>
+  </si>
+  <si>
+    <t>03.254.920/0001-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">CANOAS </t>
   </si>
   <si>
+    <t>27.047.114/0001-43</t>
+  </si>
+  <si>
     <t xml:space="preserve">ADDRESS SAVASSI </t>
   </si>
   <si>
+    <t>01.322.091/0001-44</t>
+  </si>
+  <si>
     <t xml:space="preserve">JARDINS DE GOIANIA </t>
   </si>
   <si>
+    <t>22.880.238/0001-91</t>
+  </si>
+  <si>
     <t>ALTO DA COLINA</t>
   </si>
   <si>
+    <t>28.902.071/0001-07</t>
+  </si>
+  <si>
     <t>OLIVER</t>
   </si>
   <si>
+    <t>13.169.118/0001-90</t>
+  </si>
+  <si>
     <t>MANATA</t>
   </si>
   <si>
+    <t>13.712.910/0001-49</t>
+  </si>
+  <si>
     <t>VIA SISTINA</t>
   </si>
   <si>
+    <t>05.143.758/0001-00</t>
+  </si>
+  <si>
     <t>MARTA MARIA SOARES</t>
   </si>
   <si>
+    <t>19.366.010/0001-73</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAFIRA </t>
   </si>
   <si>
+    <t>05.376.393/0001-56</t>
+  </si>
+  <si>
     <t>AMARO LANARI</t>
   </si>
   <si>
+    <t>40.849.079/0001-44</t>
+  </si>
+  <si>
     <t xml:space="preserve">SIERRA NEGRA </t>
   </si>
   <si>
+    <t>02.321.025/0001-12</t>
+  </si>
+  <si>
     <t>NERINA</t>
   </si>
   <si>
+    <t>04.755.078/0001-77</t>
+  </si>
+  <si>
     <t>SAINT MICHEL</t>
   </si>
   <si>
+    <t>08.983.864/0001-82</t>
+  </si>
+  <si>
     <t>CONDE PRADOS</t>
   </si>
   <si>
+    <t>19.765.274/0001-08</t>
+  </si>
+  <si>
     <t>JANE</t>
   </si>
   <si>
+    <t>42.777.748/0001-45</t>
+  </si>
+  <si>
     <t>SEVERINO ROSA</t>
   </si>
   <si>
+    <t>04.205.295/0001-93</t>
+  </si>
+  <si>
     <t>GENEVE</t>
   </si>
   <si>
+    <t>21.541.925/0001-10</t>
+  </si>
+  <si>
     <t>LEONARDO AUGUSTO</t>
   </si>
   <si>
+    <t>07.251.186/0001-09</t>
+  </si>
+  <si>
     <t>MICHELANGELO</t>
   </si>
   <si>
+    <t>12.632.994/0001-48</t>
+  </si>
+  <si>
     <t>ORLANDO LEMBI</t>
   </si>
   <si>
+    <t>42.765.420/0001-09</t>
+  </si>
+  <si>
     <t>DAKAR</t>
   </si>
   <si>
+    <t>02.396.217/0001-98</t>
+  </si>
+  <si>
     <t xml:space="preserve">SAO FRANCISCO </t>
   </si>
   <si>
+    <t>11.296.797/0001-32</t>
+  </si>
+  <si>
+    <t>42.777.110/0001-04</t>
+  </si>
+  <si>
     <t>DIAMOND</t>
   </si>
   <si>
+    <t>31.809.152/0001-63</t>
+  </si>
+  <si>
     <t xml:space="preserve">DUQUE DE TRIESTE </t>
   </si>
   <si>
+    <t>04.036.494/0001-15</t>
+  </si>
+  <si>
     <t>JARDIM ESMERALDA</t>
   </si>
   <si>
+    <t>51.105.032/0001-92</t>
+  </si>
+  <si>
     <t>DOM RAFAEL</t>
   </si>
   <si>
+    <t>07.154.166/0001-01</t>
+  </si>
+  <si>
+    <t>SOLAR DOS OLIVEIRA</t>
+  </si>
+  <si>
+    <t>05.651.829/0001-78</t>
+  </si>
+  <si>
     <t>D'ALGARVE</t>
   </si>
   <si>
+    <t>07.092.590/0001-79</t>
+  </si>
+  <si>
     <t xml:space="preserve">VARGINHA </t>
   </si>
   <si>
+    <t>01.987.063/0001-46</t>
+  </si>
+  <si>
     <t>OTAVIO DE MEDEIROS</t>
   </si>
   <si>
+    <t>86.942.620/0001-65</t>
+  </si>
+  <si>
     <t xml:space="preserve">LIBERTA </t>
   </si>
   <si>
+    <t>08.585.392/0001-00</t>
+  </si>
+  <si>
     <t>FLAVIO CARDOSO</t>
   </si>
   <si>
+    <t>02.428.293/0001-38</t>
+  </si>
+  <si>
     <t>MONTE BRANCO</t>
   </si>
   <si>
+    <t>05.098.992/0001-55</t>
+  </si>
+  <si>
     <t xml:space="preserve">GROPIUS </t>
   </si>
   <si>
+    <t>65.169.906/0001-80</t>
+  </si>
+  <si>
     <t xml:space="preserve">RIO GRANDE </t>
   </si>
   <si>
+    <t>10.360.822/0001-37</t>
+  </si>
+  <si>
+    <t>CONQUISTA ALVORADA</t>
+  </si>
+  <si>
+    <t>60.345.361/0001-00</t>
+  </si>
+  <si>
     <t>TOP VILLAGE</t>
   </si>
   <si>
+    <t>21.270.177/0001-88</t>
+  </si>
+  <si>
     <t>MONTE MORIAH</t>
   </si>
   <si>
+    <t>01.335.712/0001-24</t>
+  </si>
+  <si>
+    <t>MOZART</t>
+  </si>
+  <si>
+    <t>63.966.805/0001-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">SIMONE </t>
   </si>
   <si>
+    <t>20.472.080/0001-95</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO P ESTANCIA ESTORIL I</t>
+  </si>
+  <si>
+    <t>04.615.718/0001-43</t>
+  </si>
+  <si>
+    <t>ESSENCE RESIDENCIAL</t>
+  </si>
+  <si>
+    <t>PLUS_PJ</t>
+  </si>
+  <si>
+    <t>63.300.262/0001-91</t>
+  </si>
+  <si>
     <t>DEIMOISELE</t>
   </si>
   <si>
+    <t>22.034.994/0001-08</t>
+  </si>
+  <si>
+    <t>TORDESILHAS</t>
+  </si>
+  <si>
+    <t>04.347.609/0001-92</t>
+  </si>
+  <si>
     <t>CINECITTA</t>
   </si>
   <si>
+    <t>18.991.104/0001-70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIETA HOOPER </t>
+  </si>
+  <si>
+    <t>22.369.419/0001-58</t>
+  </si>
+  <si>
     <t xml:space="preserve">JOAO GONTIJO </t>
   </si>
   <si>
+    <t>18.117.355/0001-20</t>
+  </si>
+  <si>
     <t>JULIA AMORIN</t>
   </si>
   <si>
+    <t>22.605.986/0001-66</t>
+  </si>
+  <si>
+    <t>BARAO RIO VERMELHO</t>
+  </si>
+  <si>
+    <t>65.178.832/0001-48</t>
+  </si>
+  <si>
     <t xml:space="preserve">CEDRO </t>
   </si>
   <si>
+    <t>00.284.793/0001-18</t>
+  </si>
+  <si>
+    <t>RESIDENCIAL DAS AMERICAS</t>
+  </si>
+  <si>
+    <t>07.925.356/0001-85</t>
+  </si>
+  <si>
     <t xml:space="preserve">LEDA RICO </t>
   </si>
   <si>
+    <t>04.693.741/0001-56</t>
+  </si>
+  <si>
     <t xml:space="preserve">MONTE VERDE </t>
   </si>
   <si>
+    <t>38.728.853/0001-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">EDMAR VIANA </t>
   </si>
   <si>
+    <t>23.235.896/0001-93</t>
+  </si>
+  <si>
     <t>RENATA</t>
   </si>
   <si>
+    <t>25.572.983/0001-61</t>
+  </si>
+  <si>
+    <t>VILLA FRATINA</t>
+  </si>
+  <si>
+    <t>17.642.214/0001-64</t>
+  </si>
+  <si>
+    <t>DADE CAVALCANTI</t>
+  </si>
+  <si>
+    <t>19.050.866/0001-35</t>
+  </si>
+  <si>
     <t>MARIA HELENA ROCHA</t>
   </si>
   <si>
+    <t>24.278.935/0001-00</t>
+  </si>
+  <si>
     <t xml:space="preserve">BOSQUE DOS ALAMOS </t>
   </si>
   <si>
+    <t>25.575.036/0001-24</t>
+  </si>
+  <si>
+    <t>MIRANTE DO TIJUCO</t>
+  </si>
+  <si>
+    <t>21.945.318/0001-15</t>
+  </si>
+  <si>
+    <t>BETINHA PEREIRA NEVES</t>
+  </si>
+  <si>
+    <t>03.966.996/0001-82</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRINCIPE CHARLES </t>
   </si>
   <si>
+    <t>25.469.529/0001-80</t>
+  </si>
+  <si>
     <t xml:space="preserve">EVA MARCONDES </t>
   </si>
   <si>
+    <t>14.001.197/0001-98</t>
+  </si>
+  <si>
     <t>MIRANTE DOS COQUEIROS</t>
   </si>
   <si>
+    <t>23.357.672/0001-54</t>
+  </si>
+  <si>
     <t>BOUGANVILE</t>
   </si>
   <si>
+    <t>22.704.899/0001-66</t>
+  </si>
+  <si>
     <t>KUARUP</t>
   </si>
   <si>
+    <t>26.265.827/0001-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">MODENESI </t>
   </si>
   <si>
+    <t>21.128.894/0001-70</t>
+  </si>
+  <si>
     <t xml:space="preserve">EMBUIA </t>
   </si>
   <si>
+    <t>04.983.270/0001-10</t>
+  </si>
+  <si>
     <t>TOP HOME</t>
   </si>
   <si>
+    <t>12.633.018/0001-00</t>
+  </si>
+  <si>
+    <t>PALAZZO DI LOURDES</t>
+  </si>
+  <si>
+    <t>12.217.846/0001-67</t>
+  </si>
+  <si>
     <t>VILA CATHARINA</t>
   </si>
   <si>
+    <t>26.306.061/0001-75</t>
+  </si>
+  <si>
     <t xml:space="preserve">MANOEL MENEZES </t>
   </si>
   <si>
-    <t xml:space="preserve">SAINT GERMAIN </t>
+    <t>355.411.806-00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALAZZO TOSCANA </t>
+  </si>
+  <si>
+    <t>17.745.564/0001-56</t>
+  </si>
+  <si>
+    <t>07.135.268/0001-80</t>
   </si>
   <si>
     <t xml:space="preserve">CRISTINA </t>
   </si>
   <si>
+    <t>02.175.679/0001-85</t>
+  </si>
+  <si>
     <t>LOGOS</t>
   </si>
   <si>
+    <t>65.166.449/0001-70</t>
+  </si>
+  <si>
     <t xml:space="preserve">TURMALINAS </t>
   </si>
   <si>
+    <t>04.474.988/0001-81</t>
+  </si>
+  <si>
     <t>SAVASSI TOWER</t>
   </si>
   <si>
+    <t>23.601.815/0001-21</t>
+  </si>
+  <si>
     <t>EL GRECO</t>
   </si>
   <si>
+    <t>13.127.310/0001-13</t>
+  </si>
+  <si>
     <t>SPAZIO TREVISO</t>
   </si>
   <si>
+    <t>28.820.416/0001-75</t>
+  </si>
+  <si>
     <t>SANT ANDRES</t>
   </si>
   <si>
+    <t>13.404.748/0001-00</t>
+  </si>
+  <si>
     <t>CELIA BOTELHO</t>
   </si>
   <si>
+    <t>10.615.467/0001-08</t>
+  </si>
+  <si>
     <t>VIRGINIA</t>
   </si>
   <si>
+    <t>02.648.771/0001-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">TRIBUNA OFFICES </t>
   </si>
   <si>
+    <t>14.001.187/0001-52</t>
+  </si>
+  <si>
     <t xml:space="preserve">VISTA CASTELA </t>
   </si>
   <si>
+    <t>27.149.291/0001-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">SOLAR OURO PRETO </t>
   </si>
   <si>
+    <t>38.724.035/0001-46</t>
+  </si>
+  <si>
     <t xml:space="preserve">LUMIERE </t>
   </si>
   <si>
+    <t>02.871.132/0001-14</t>
+  </si>
+  <si>
     <t>ROMA</t>
   </si>
   <si>
-    <t xml:space="preserve">TORRES DO HORIZONTE </t>
+    <t>65.156.903/0001-01</t>
+  </si>
+  <si>
+    <t>23.509.783/0001-39</t>
   </si>
   <si>
     <t>BH-TEC</t>
   </si>
   <si>
+    <t>07.624.772/0001-43</t>
+  </si>
+  <si>
     <t>ALTO ANCHIETA</t>
   </si>
   <si>
+    <t>48.675.181/0001-82</t>
+  </si>
+  <si>
     <t xml:space="preserve">QUINTAS DO CARMO </t>
   </si>
   <si>
+    <t>03.441.244/0001-06</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAMPEZZO </t>
   </si>
   <si>
+    <t>18.333.743/0001-49</t>
+  </si>
+  <si>
     <t>JOAO CARVALHO</t>
   </si>
   <si>
+    <t>65.178.816/0001-55</t>
+  </si>
+  <si>
     <t>CENTRO COMERCIAL SAVASSI</t>
   </si>
   <si>
+    <t>04.186.922/0001-96</t>
+  </si>
+  <si>
     <t xml:space="preserve">FAENA OFICES </t>
   </si>
   <si>
+    <t>30.782.974/0001-35</t>
+  </si>
+  <si>
     <t>CORDOBA</t>
   </si>
   <si>
+    <t>00.318.181/0001-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAMPO DE FIORI </t>
   </si>
   <si>
+    <t>20.207.631/0001-93</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALDA BRANT </t>
   </si>
   <si>
+    <t>24.960.240/0001-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARLOS GOMES </t>
   </si>
   <si>
+    <t>65.181.398/0001-55</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARIANE </t>
   </si>
   <si>
+    <t>11.058.806/0001-57</t>
+  </si>
+  <si>
+    <t>ALPHAVILLE LAGOA DOS INGLESES</t>
+  </si>
+  <si>
+    <t>PLUS-BRA</t>
+  </si>
+  <si>
+    <t>97.519.238/0001-60</t>
+  </si>
+  <si>
+    <t>01.536.757/0001-67</t>
+  </si>
+  <si>
+    <t>BELLA VITA STUDIO</t>
+  </si>
+  <si>
+    <t>04.851.040/0001-06</t>
+  </si>
+  <si>
     <t>CENTAURUS</t>
   </si>
   <si>
+    <t>38.729.653/0001-89</t>
+  </si>
+  <si>
     <t>LAGOA IMPERIAL</t>
   </si>
   <si>
+    <t>31.566.021/0001-00</t>
+  </si>
+  <si>
     <t>SAMUEL ROMANO</t>
   </si>
   <si>
+    <t>31.072.666/0001-89</t>
+  </si>
+  <si>
     <t>LUCIANA MAIA GONCALVES</t>
   </si>
   <si>
+    <t>07.283.976/0001-68</t>
+  </si>
+  <si>
     <t>DOM MICHELANGELO DEI CONTI</t>
   </si>
   <si>
+    <t>01.896.451/0001-11</t>
+  </si>
+  <si>
     <t xml:space="preserve">IEDA </t>
   </si>
   <si>
-    <t>CLAUDIA</t>
+    <t>05.653.703/0001-32</t>
+  </si>
+  <si>
+    <t>23.841.398/0001-94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51 GARDEN PARK </t>
+  </si>
+  <si>
+    <t>01.313.829/0001-07</t>
+  </si>
+  <si>
+    <t>BASILEA</t>
+  </si>
+  <si>
+    <t>07.250.252/0001-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONT BLANC </t>
+  </si>
+  <si>
+    <t>42.778.597/0001-40</t>
   </si>
   <si>
     <t xml:space="preserve">CORINTO </t>
   </si>
   <si>
+    <t>25.573.635/0001-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">SION </t>
   </si>
   <si>
+    <t>38.738.761/0001-18</t>
+  </si>
+  <si>
     <t xml:space="preserve">SILVINO MATTOS </t>
   </si>
   <si>
+    <t>19.121.203/0001-64</t>
+  </si>
+  <si>
     <t>RIVIERA DI MONACO</t>
   </si>
   <si>
+    <t>18.945.495/0001-97</t>
+  </si>
+  <si>
     <t xml:space="preserve">IMPERIAL CENTER </t>
   </si>
   <si>
+    <t>73.895.104/0001-85</t>
+  </si>
+  <si>
     <t>ISAURA LOPES GUIMARAES</t>
   </si>
   <si>
+    <t>31.204.148/0001-71</t>
+  </si>
+  <si>
     <t xml:space="preserve">ROYAL CENTER </t>
   </si>
   <si>
+    <t>02.998.681/0001-54</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARMANDO MENDES </t>
   </si>
   <si>
+    <t>17.570.431/0001-96</t>
+  </si>
+  <si>
     <t>RIGUEIRA HISSA</t>
   </si>
   <si>
+    <t>28.078.338/0001-85</t>
+  </si>
+  <si>
     <t>SERRA DOS MANACAS</t>
   </si>
   <si>
-    <t>COD</t>
-  </si>
-  <si>
-    <t>CONDOMINIO</t>
-  </si>
-  <si>
-    <t>CNPJ</t>
-  </si>
-  <si>
-    <t>SAO CARLOS</t>
-  </si>
-  <si>
-    <t>05.098.992/0001-55</t>
-  </si>
-  <si>
-    <t>65.169.906/0001-80</t>
-  </si>
-  <si>
-    <t>10.360.822/0001-37</t>
-  </si>
-  <si>
-    <t>21.270.177/0001-88</t>
-  </si>
-  <si>
-    <t>01.335.712/0001-24</t>
-  </si>
-  <si>
-    <t>20.472.080/0001-95</t>
-  </si>
-  <si>
-    <t>04.615.718/0001-43</t>
-  </si>
-  <si>
-    <t>22.034.994/0001-08</t>
-  </si>
-  <si>
-    <t>18.991.104/0001-70</t>
-  </si>
-  <si>
-    <t>22.369.419/0001-58</t>
-  </si>
-  <si>
-    <t>18.117.355/0001-20</t>
-  </si>
-  <si>
-    <t>22.605.986/0001-66</t>
-  </si>
-  <si>
-    <t>00.284.793/0001-18</t>
-  </si>
-  <si>
-    <t>04.693.741/0001-56</t>
-  </si>
-  <si>
-    <t>38.728.853/0001-17</t>
-  </si>
-  <si>
-    <t>23.235.896/0001-93</t>
-  </si>
-  <si>
-    <t>25.572.983/0001-61</t>
-  </si>
-  <si>
-    <t>19.050.866/0001-35</t>
-  </si>
-  <si>
-    <t>24.278.935/0001-00</t>
-  </si>
-  <si>
-    <t>25.575.036/0001-24</t>
-  </si>
-  <si>
-    <t>21.945.318/0001-15</t>
-  </si>
-  <si>
-    <t>03.966.996/0001-82</t>
-  </si>
-  <si>
-    <t>25.469.529/0001-80</t>
-  </si>
-  <si>
-    <t>14.001.197/0001-98</t>
-  </si>
-  <si>
-    <t>23.357.672/0001-54</t>
-  </si>
-  <si>
-    <t>22.704.899/0001-66</t>
-  </si>
-  <si>
-    <t>26.265.827/0001-10</t>
-  </si>
-  <si>
-    <t>21.128.894/0001-70</t>
-  </si>
-  <si>
-    <t>04.983.270/0001-10</t>
-  </si>
-  <si>
-    <t>12.633.018/0001-00</t>
-  </si>
-  <si>
-    <t>12.217.846/0001-67</t>
-  </si>
-  <si>
-    <t>26.306.061/0001-75</t>
-  </si>
-  <si>
-    <t>355.411.806-00</t>
-  </si>
-  <si>
-    <t>17.745.564/0001-56</t>
-  </si>
-  <si>
-    <t>07.135.268/0001-80</t>
-  </si>
-  <si>
-    <t>02.175.679/0001-85</t>
-  </si>
-  <si>
-    <t>65.166.449/0001-70</t>
-  </si>
-  <si>
-    <t>04.474.988/0001-81</t>
-  </si>
-  <si>
-    <t>23.601.815/0001-21</t>
-  </si>
-  <si>
-    <t>13.127.310/0001-13</t>
-  </si>
-  <si>
-    <t>28.820.416/0001-75</t>
-  </si>
-  <si>
-    <t>13.404.748/0001-00</t>
-  </si>
-  <si>
-    <t>10.615.467/0001-08</t>
-  </si>
-  <si>
-    <t>02.648.771/0001-15</t>
-  </si>
-  <si>
-    <t>14.001.187/0001-52</t>
-  </si>
-  <si>
-    <t>27.149.291/0001-30</t>
-  </si>
-  <si>
-    <t>38.724.035/0001-46</t>
-  </si>
-  <si>
-    <t>02.871.132/0001-14</t>
-  </si>
-  <si>
-    <t>65.156.903/0001-01</t>
-  </si>
-  <si>
-    <t>23.509.783/0001-39</t>
-  </si>
-  <si>
-    <t>07.624.772/0001-43</t>
-  </si>
-  <si>
-    <t>48.675.181/0001-82</t>
-  </si>
-  <si>
-    <t>03.441.244/0001-06</t>
-  </si>
-  <si>
-    <t>18.333.743/0001-49</t>
-  </si>
-  <si>
-    <t>65.178.816/0001-55</t>
-  </si>
-  <si>
-    <t>04.186.922/0001-96</t>
-  </si>
-  <si>
-    <t>30.782.974/0001-35</t>
-  </si>
-  <si>
-    <t>00.318.181/0001-07</t>
-  </si>
-  <si>
-    <t>20.207.631/0001-93</t>
-  </si>
-  <si>
-    <t>24.960.240/0001-04</t>
-  </si>
-  <si>
-    <t>65.181.398/0001-55</t>
-  </si>
-  <si>
-    <t>11.058.806/0001-57</t>
-  </si>
-  <si>
-    <t>97.519.238/0001-60</t>
-  </si>
-  <si>
-    <t>01.536.757/0001-67</t>
-  </si>
-  <si>
-    <t>04.851.040/0001-06</t>
-  </si>
-  <si>
-    <t>38.729.653/0001-89</t>
-  </si>
-  <si>
-    <t>31.566.021/0001-00</t>
-  </si>
-  <si>
-    <t>31.072.666/0001-89</t>
-  </si>
-  <si>
-    <t>07.283.976/0001-68</t>
-  </si>
-  <si>
-    <t>01.896.451/0001-11</t>
-  </si>
-  <si>
-    <t>05.653.703/0001-32</t>
-  </si>
-  <si>
-    <t>23.841.398/0001-94</t>
-  </si>
-  <si>
-    <t>01.313.829/0001-07</t>
-  </si>
-  <si>
-    <t>07.250.252/0001-18</t>
-  </si>
-  <si>
-    <t>42.778.597/0001-40</t>
-  </si>
-  <si>
-    <t>25.573.635/0001-09</t>
-  </si>
-  <si>
-    <t>38.738.761/0001-18</t>
-  </si>
-  <si>
-    <t>19.121.203/0001-64</t>
-  </si>
-  <si>
-    <t>18.945.495/0001-97</t>
-  </si>
-  <si>
-    <t>73.895.104/0001-85</t>
-  </si>
-  <si>
-    <t>31.204.148/0001-71</t>
-  </si>
-  <si>
-    <t>02.998.681/0001-54</t>
-  </si>
-  <si>
-    <t>17.570.431/0001-96</t>
-  </si>
-  <si>
-    <t>28.078.338/0001-85</t>
-  </si>
-  <si>
-    <t>19.270.149/0001-19</t>
-  </si>
-  <si>
-    <t>38.419.086/0001-64</t>
-  </si>
-  <si>
-    <t>26.388.793/0001-51</t>
-  </si>
-  <si>
-    <t>26.232.066/0001-09</t>
-  </si>
-  <si>
-    <t>25.530.528/0001-01</t>
-  </si>
-  <si>
-    <t>65.148.751/0001-03</t>
-  </si>
-  <si>
-    <t>65.143.075/0001-77</t>
-  </si>
-  <si>
-    <t>42.788.919/0001-31</t>
-  </si>
-  <si>
-    <t>20.473.187/0001-58</t>
-  </si>
-  <si>
-    <t>25.468.778/0001-50</t>
-  </si>
-  <si>
-    <t>25.568.882/0001-17</t>
-  </si>
-  <si>
-    <t>02.173.659/0001-75</t>
-  </si>
-  <si>
-    <t>38.741.526/0001-03</t>
-  </si>
-  <si>
-    <t>42.778.878/0001-00</t>
-  </si>
-  <si>
-    <t>00.494.979/0001-00</t>
-  </si>
-  <si>
-    <t>42.779.744/0001-04</t>
-  </si>
-  <si>
-    <t>86.839.859/0001-04</t>
-  </si>
-  <si>
-    <t>42.764.399/0001-27</t>
-  </si>
-  <si>
-    <t>12.513.839/0001-02</t>
-  </si>
-  <si>
-    <t>03.023.476/0001-36</t>
-  </si>
-  <si>
-    <t>65.158.586/0001-62</t>
-  </si>
-  <si>
-    <t>00.740.218/0001-82</t>
-  </si>
-  <si>
-    <t>00.906.063/0001-01</t>
-  </si>
-  <si>
-    <t>02.651.835/0001-37</t>
-  </si>
-  <si>
-    <t>26.385.054/0001-06</t>
-  </si>
-  <si>
-    <t>01.335.765/0001-45</t>
-  </si>
-  <si>
-    <t>00.931.382/0001-77</t>
-  </si>
-  <si>
-    <t>01.774.760/0001-19</t>
-  </si>
-  <si>
-    <t>03.606.174/0001-90</t>
-  </si>
-  <si>
-    <t>42.765.362/0001-13</t>
-  </si>
-  <si>
-    <t>09.069.496/0001-24</t>
-  </si>
-  <si>
-    <t>11.177.026/0001-26</t>
-  </si>
-  <si>
-    <t>00.697.217/0001-00</t>
-  </si>
-  <si>
-    <t>00.639.590/0001-05</t>
-  </si>
-  <si>
-    <t>70.953.575/0001-04</t>
-  </si>
-  <si>
-    <t>20.999.819/0001-11</t>
-  </si>
-  <si>
-    <t>42.763.722/0001-48</t>
-  </si>
-  <si>
-    <t>70.956.867/0001-09</t>
-  </si>
-  <si>
-    <t>65.170.763/0001-26</t>
-  </si>
-  <si>
-    <t>07.235.068/0001-07</t>
-  </si>
-  <si>
-    <t>40.484.041/0001-15</t>
-  </si>
-  <si>
-    <t>00.116.412/0001-91</t>
-  </si>
-  <si>
-    <t>01.971.539/0001-50</t>
-  </si>
-  <si>
-    <t>03.058.185/0001-83</t>
-  </si>
-  <si>
-    <t>03.245.064/0001-40</t>
-  </si>
-  <si>
-    <t>02.291.972/0001-08</t>
-  </si>
-  <si>
-    <t>02.712.276/0001-28</t>
-  </si>
-  <si>
-    <t>65.162.430/0001-55</t>
-  </si>
-  <si>
-    <t>00.143.954/0001-53</t>
-  </si>
-  <si>
-    <t>42.767.475/0001-58</t>
-  </si>
-  <si>
-    <t>03.558.818/0001-12</t>
-  </si>
-  <si>
-    <t>65.177.339/0001-03</t>
-  </si>
-  <si>
-    <t>20.473.161/0001-00</t>
-  </si>
-  <si>
-    <t>97.491.260/0001-49</t>
-  </si>
-  <si>
-    <t>02.028.860/0001-69</t>
-  </si>
-  <si>
-    <t>34.429.769/0001-41</t>
-  </si>
-  <si>
-    <t>42.771.766/0001-10</t>
-  </si>
-  <si>
-    <t>21.507.371/0001-34</t>
-  </si>
-  <si>
-    <t>11.867.583/0001-79</t>
-  </si>
-  <si>
-    <t>04.338.277/0001-80</t>
-  </si>
-  <si>
-    <t>03.085.700/0001-14</t>
-  </si>
-  <si>
-    <t>97.424.295/0001-65</t>
-  </si>
-  <si>
-    <t>00.098.286/0001-90</t>
-  </si>
-  <si>
-    <t>24.025.801/0001-70</t>
-  </si>
-  <si>
-    <t>73.878.951/0001-31</t>
-  </si>
-  <si>
-    <t>08.041.935/0001-28</t>
-  </si>
-  <si>
-    <t>00.708.692/0001-27</t>
-  </si>
-  <si>
-    <t>33.497.533/0001-80</t>
-  </si>
-  <si>
-    <t>10.966.799/0001-29</t>
-  </si>
-  <si>
-    <t>25.572.470/0001-50</t>
-  </si>
-  <si>
-    <t>02.312.855/0001-83</t>
-  </si>
-  <si>
-    <t>01.383.665/0001-94</t>
-  </si>
-  <si>
-    <t>25.455.262/0001-71</t>
-  </si>
-  <si>
-    <t>04.114.656/0001-96</t>
-  </si>
-  <si>
-    <t>04.247.555/0001-93</t>
-  </si>
-  <si>
-    <t>16.842.756/0001-18</t>
-  </si>
-  <si>
-    <t>01.067.088/0001-21</t>
-  </si>
-  <si>
-    <t>04.275.179/0001-40</t>
-  </si>
-  <si>
-    <t>42.784.769/0001-98</t>
-  </si>
-  <si>
-    <t>65.145.518/0001-69</t>
-  </si>
-  <si>
-    <t>02.202.492/0001-23</t>
-  </si>
-  <si>
-    <t>05.080.984/0001-81</t>
-  </si>
-  <si>
-    <t>70.946.108/0001-57</t>
-  </si>
-  <si>
-    <t>07.135.705/0001-65</t>
-  </si>
-  <si>
-    <t>65.156.861/0001-09</t>
-  </si>
-  <si>
-    <t>01.482.514/0001-93</t>
-  </si>
-  <si>
-    <t>05.085.456/0001-15</t>
-  </si>
-  <si>
-    <t>65.181.638/0001-11</t>
-  </si>
-  <si>
-    <t>01.806.572/0001-25</t>
-  </si>
-  <si>
-    <t>23.217.664/0001-02</t>
-  </si>
-  <si>
-    <t>05.082.435/0001-46</t>
-  </si>
-  <si>
-    <t>01.195.567/0001-23</t>
-  </si>
-  <si>
-    <t>04.870.726/0001-36</t>
-  </si>
-  <si>
-    <t>00.867.641/0001-48</t>
-  </si>
-  <si>
-    <t>74.148.420/0001-56</t>
-  </si>
-  <si>
-    <t>65.152.126/0001-27</t>
-  </si>
-  <si>
-    <t>02.232.226/0001-43</t>
-  </si>
-  <si>
-    <t>25.704.115/0001-98</t>
-  </si>
-  <si>
-    <t>08.811.255/0001-46</t>
-  </si>
-  <si>
-    <t>05.629.236/0001-05</t>
-  </si>
-  <si>
-    <t>26.231.985/0001-50</t>
-  </si>
-  <si>
-    <t>03.150.555/0001-08</t>
-  </si>
-  <si>
-    <t>26.231.019/0001-32</t>
-  </si>
-  <si>
-    <t>07.572.539/0001-64</t>
-  </si>
-  <si>
-    <t>06.049.617/0001-88</t>
-  </si>
-  <si>
-    <t>74.053.810/0001-42</t>
-  </si>
-  <si>
-    <t>71.089.122/0001-44</t>
-  </si>
-  <si>
-    <t>04.398.998/0001-85</t>
-  </si>
-  <si>
-    <t>86.692.787/0001-15</t>
-  </si>
-  <si>
-    <t>20.446.647/0001-59</t>
-  </si>
-  <si>
-    <t>06.375.532/0001-90</t>
-  </si>
-  <si>
-    <t>00.639.593/0001-30</t>
-  </si>
-  <si>
-    <t>02.229.281/0001-84</t>
-  </si>
-  <si>
-    <t>02.701.075/0001-25</t>
-  </si>
-  <si>
-    <t>04.170.257/0001-42</t>
-  </si>
-  <si>
-    <t>05.350.922/0001-42</t>
-  </si>
-  <si>
-    <t>29.536.510/0001-60</t>
-  </si>
-  <si>
-    <t>00.479.772/0001-58</t>
-  </si>
-  <si>
-    <t>65.180.440/0001-13</t>
-  </si>
-  <si>
-    <t>40.119.057/0001-29</t>
-  </si>
-  <si>
-    <t>25.695.040/0001-26</t>
-  </si>
-  <si>
-    <t>65.164.857/0001-92</t>
-  </si>
-  <si>
-    <t>05.230.129/0001-00</t>
-  </si>
-  <si>
-    <t>26.387.464/0001-96</t>
-  </si>
-  <si>
-    <t>25.693.474/0001-97</t>
-  </si>
-  <si>
-    <t>01.118.248/0001-14</t>
-  </si>
-  <si>
-    <t>08.109.602/0001-93</t>
-  </si>
-  <si>
-    <t>00.327.946/0001-67</t>
-  </si>
-  <si>
-    <t>07.547.257/0001-07</t>
-  </si>
-  <si>
-    <t>74.119.892/0001-80</t>
-  </si>
-  <si>
-    <t>19.792.399/0001-19</t>
-  </si>
-  <si>
-    <t>00.745.384/0001-71</t>
-  </si>
-  <si>
-    <t>01.564.428/0001-20</t>
-  </si>
-  <si>
-    <t>00.177.244/0001-44</t>
-  </si>
-  <si>
-    <t>01.502.972/0001-47</t>
-  </si>
-  <si>
-    <t>42.786.970/0001-04</t>
-  </si>
-  <si>
-    <t>70.954.375/0001-76</t>
-  </si>
-  <si>
-    <t>02.940.446/0001-21</t>
-  </si>
-  <si>
-    <t>02.243.971/0001-98</t>
-  </si>
-  <si>
-    <t>02.972.746/0001-92</t>
-  </si>
-  <si>
-    <t>65.144.800/0001-21</t>
-  </si>
-  <si>
-    <t>70.942.610/0001-90</t>
-  </si>
-  <si>
-    <t>73.314.163/0001-12</t>
-  </si>
-  <si>
-    <t>38.739.330/0001-76</t>
-  </si>
-  <si>
-    <t>00.745.388/0001-50</t>
-  </si>
-  <si>
-    <t>36.669.550/0001-45</t>
-  </si>
-  <si>
-    <t>11.808.031/0001-90</t>
-  </si>
-  <si>
-    <t>00.434.396/0001-85</t>
-  </si>
-  <si>
-    <t>10.949.264/0001-40</t>
-  </si>
-  <si>
-    <t>08.935.490/0001-20</t>
-  </si>
-  <si>
-    <t>12.482.928/0001-39</t>
-  </si>
-  <si>
-    <t>00.385.739/0001-69</t>
-  </si>
-  <si>
-    <t>01.906.498/0001-19</t>
-  </si>
-  <si>
-    <t>03.077.558/0001-63</t>
-  </si>
-  <si>
-    <t>70.951.181/0001-17</t>
-  </si>
-  <si>
-    <t>08.951.158/0001-59</t>
-  </si>
-  <si>
-    <t>10.372.475/0001-62</t>
-  </si>
-  <si>
-    <t>65.150.773/0001-08</t>
-  </si>
-  <si>
-    <t>02.798.012/0001-39</t>
-  </si>
-  <si>
-    <t>04.479.304/0001-34</t>
-  </si>
-  <si>
-    <t>12.641.671/0001-10</t>
-  </si>
-  <si>
-    <t>12.126.907/0001-80</t>
-  </si>
-  <si>
-    <t>12.258.948/0001-20</t>
-  </si>
-  <si>
-    <t>26.229.724/0001-03</t>
-  </si>
-  <si>
-    <t>05.738.382/0001-79</t>
-  </si>
-  <si>
-    <t>13.299.611/0001-24</t>
-  </si>
-  <si>
-    <t>25.568.528/0001-92</t>
-  </si>
-  <si>
-    <t>65.151.862/0001-60</t>
-  </si>
-  <si>
-    <t>26.388.969/0001-75</t>
-  </si>
-  <si>
-    <t>65.148.728/0001-00</t>
-  </si>
-  <si>
-    <t>04.815.709/0001-04</t>
-  </si>
-  <si>
-    <t>05.241.115/0001-91</t>
-  </si>
-  <si>
-    <t>74.025.792/0001-95</t>
-  </si>
-  <si>
-    <t>03.254.920/0001-24</t>
-  </si>
-  <si>
-    <t>27.047.114/0001-43</t>
-  </si>
-  <si>
-    <t>01.322.091/0001-44</t>
-  </si>
-  <si>
-    <t>22.880.238/0001-91</t>
-  </si>
-  <si>
-    <t>28.902.071/0001-07</t>
-  </si>
-  <si>
-    <t>13.169.118/0001-90</t>
-  </si>
-  <si>
-    <t>13.712.910/0001-49</t>
-  </si>
-  <si>
-    <t>05.143.758/0001-00</t>
-  </si>
-  <si>
-    <t>19.366.010/0001-73</t>
-  </si>
-  <si>
-    <t>05.376.393/0001-56</t>
-  </si>
-  <si>
-    <t>40.849.079/0001-44</t>
-  </si>
-  <si>
-    <t>02.321.025/0001-12</t>
-  </si>
-  <si>
-    <t>04.755.078/0001-77</t>
-  </si>
-  <si>
-    <t>08.983.864/0001-82</t>
-  </si>
-  <si>
-    <t>19.765.274/0001-08</t>
-  </si>
-  <si>
-    <t>42.777.748/0001-45</t>
-  </si>
-  <si>
-    <t>04.205.295/0001-93</t>
-  </si>
-  <si>
-    <t>21.541.925/0001-10</t>
-  </si>
-  <si>
-    <t>07.251.186/0001-09</t>
-  </si>
-  <si>
-    <t>12.632.994/0001-48</t>
-  </si>
-  <si>
-    <t>42.765.420/0001-09</t>
-  </si>
-  <si>
-    <t>02.396.217/0001-98</t>
-  </si>
-  <si>
-    <t>11.296.797/0001-32</t>
-  </si>
-  <si>
-    <t>42.777.110/0001-04</t>
-  </si>
-  <si>
-    <t>31.809.152/0001-63</t>
-  </si>
-  <si>
-    <t>04.036.494/0001-15</t>
-  </si>
-  <si>
-    <t>51.105.032/0001-92</t>
-  </si>
-  <si>
-    <t>07.154.166/0001-01</t>
-  </si>
-  <si>
-    <t>05.651.829/0001-78</t>
-  </si>
-  <si>
-    <t>07.092.590/0001-79</t>
-  </si>
-  <si>
-    <t>01.987.063/0001-46</t>
-  </si>
-  <si>
-    <t>86.942.620/0001-65</t>
-  </si>
-  <si>
-    <t>08.585.392/0001-00</t>
-  </si>
-  <si>
-    <t>02.428.293/0001-38</t>
-  </si>
-  <si>
     <t>00.627.891/0001-00</t>
   </si>
   <si>
-    <t>PLUS</t>
-  </si>
-  <si>
-    <t>FOLHA</t>
-  </si>
-  <si>
-    <t>GESTORA</t>
-  </si>
-  <si>
-    <t>CAMILA CAETANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUADALUPE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAMOND ARCH </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUTHER KING </t>
-  </si>
-  <si>
-    <t>DR. HELADIO J MARTINS</t>
-  </si>
-  <si>
-    <t>TERESINHA BRANDAO RESENDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOWN HOUSE </t>
-  </si>
-  <si>
-    <t>ASSOCIACAO P ESTANCIA ESTORIL I</t>
-  </si>
-  <si>
-    <t>CHEQUE</t>
-  </si>
-  <si>
-    <t>GESTAO</t>
-  </si>
-  <si>
-    <t>PLUS-SIC</t>
-  </si>
-  <si>
-    <t>PLUS-CEF</t>
-  </si>
-  <si>
-    <t>PLUS-PJ</t>
-  </si>
-  <si>
-    <t>PLUS-BRA</t>
-  </si>
-  <si>
-    <t>C_EMITE</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL CHAVES CANCADO</t>
-  </si>
-  <si>
-    <t>23.168.225/0001-57</t>
-  </si>
-  <si>
-    <t>RESIDENCIAL LIMA ROSA</t>
-  </si>
-  <si>
-    <t>34.504.252/0001-70</t>
-  </si>
-  <si>
-    <t>MARYSE</t>
-  </si>
-  <si>
-    <t>20.185.989/0001-62</t>
-  </si>
-  <si>
-    <t>CASABLANCA</t>
-  </si>
-  <si>
-    <t>10.771.643/0001-92</t>
-  </si>
-  <si>
-    <t>DIAMANTE</t>
-  </si>
-  <si>
-    <t>04.100.983/0001-99</t>
-  </si>
-  <si>
-    <t>PALMARES</t>
-  </si>
-  <si>
-    <t>29.457.416/0001-15</t>
-  </si>
-  <si>
-    <t>ANTONIO PEDRO MACIEL</t>
-  </si>
-  <si>
-    <t>05.217.866/0001-72</t>
-  </si>
-  <si>
-    <t>AZURITA</t>
-  </si>
-  <si>
-    <t>JOSE MARTINS DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>MARIA LUIZA</t>
-  </si>
-  <si>
-    <t>PALAIS DE VERSAILLES</t>
-  </si>
-  <si>
-    <t>20.461.885/0001-33</t>
-  </si>
-  <si>
-    <t>03.069.991/0001-57</t>
-  </si>
-  <si>
-    <t>04.904.825/0001-91</t>
-  </si>
-  <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>56.226.238/0001-94</t>
-  </si>
-  <si>
-    <t>IPE</t>
-  </si>
-  <si>
-    <t>23.971.443/0001-25</t>
-  </si>
-  <si>
-    <t>00.568.356/0001-26</t>
-  </si>
-  <si>
-    <t>DOM LUCCILIO</t>
-  </si>
-  <si>
-    <t>38.727.624/0001-88</t>
-  </si>
-  <si>
-    <t>PAULO EDUARDO</t>
-  </si>
-  <si>
-    <t>57.490.281/0001-25</t>
-  </si>
-  <si>
-    <t>04.558.217/0001-72</t>
-  </si>
-  <si>
-    <t>LA CORUNA</t>
-  </si>
-  <si>
-    <t>48.922.623/0001-48</t>
-  </si>
-  <si>
-    <t>MARCIA HELENA</t>
-  </si>
-  <si>
-    <t>ANTONIO MOURA</t>
-  </si>
-  <si>
-    <t>15.045.757/0001-79</t>
-  </si>
-  <si>
-    <t>42.772.103/0001-10</t>
-  </si>
-  <si>
-    <t>42.781.542/0001-99</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>70.955.836/0001-25</t>
-  </si>
-  <si>
-    <t>13.471.226/0001-12</t>
-  </si>
-  <si>
-    <t>RAJA PLUS</t>
-  </si>
-  <si>
-    <t>44.594.887/0001-69</t>
-  </si>
-  <si>
-    <t>RESERVA LAGUNA</t>
-  </si>
-  <si>
-    <t>55.066.652/0001-10</t>
-  </si>
-  <si>
-    <t>DADE CAVALCANTI</t>
-  </si>
-  <si>
-    <t>42.765.305/0001-34</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>73.516.023/0001-27</t>
-  </si>
-  <si>
-    <t>DIOGO VASCONCELOS</t>
-  </si>
-  <si>
-    <t>65.167.967/0001-08</t>
-  </si>
-  <si>
-    <t>INTERPARK</t>
-  </si>
-  <si>
-    <t>01.201.299/0001-05</t>
-  </si>
-  <si>
-    <t>CACUERA</t>
-  </si>
-  <si>
-    <t>60.620.800/0001-37</t>
-  </si>
-  <si>
-    <t>RESERVA DAS PALMEIRAS</t>
-  </si>
-  <si>
-    <t>60.521.832/0001-85</t>
-  </si>
-  <si>
-    <t>ALTHA DORTMUND</t>
-  </si>
-  <si>
-    <t>30.708.225/0001-68</t>
-  </si>
-  <si>
-    <t>01.656.186/0001-02</t>
-  </si>
-  <si>
-    <t>SAN PELINO</t>
-  </si>
-  <si>
-    <t>02.693.218/0001-02</t>
-  </si>
-  <si>
-    <t>SERRA DOS PINHAIS</t>
-  </si>
-  <si>
-    <t>52.081.752/0001-28</t>
-  </si>
-  <si>
-    <t>JONAS BELIZARIO</t>
-  </si>
-  <si>
-    <t>26.269.738/0001-42</t>
-  </si>
-  <si>
-    <t>AGUAS CLARAS</t>
-  </si>
-  <si>
-    <t>42.775.312/0001-17</t>
-  </si>
-  <si>
-    <t>ALPHAVILLE LAGOA DOS INGLESES</t>
-  </si>
-  <si>
-    <t>BELLA VITA STUDIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DM CABRAL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARISTEU MUSCHIONI </t>
-  </si>
-  <si>
-    <t>ANITA CIOLETTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARINHO M MENDONCA </t>
-  </si>
-  <si>
-    <t>CAMPOS ELISEOS</t>
-  </si>
-  <si>
-    <t>ELPIDIO CORDEIRO DO COUTO</t>
-  </si>
-  <si>
-    <t>MARCOLLA</t>
-  </si>
-  <si>
-    <t>JOAO LUIZ DE FREITAS</t>
-  </si>
-  <si>
-    <t>EVERARDO VIEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTO BELLO </t>
-  </si>
-  <si>
-    <t>ANTONIO DE CASTRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VILLE FRANCHE </t>
-  </si>
-  <si>
-    <t>PORTA D'ORO</t>
-  </si>
-  <si>
-    <t>SAINT HONORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAUL CEZZANNE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VOLPI SION </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RACHEL COHEN </t>
-  </si>
-  <si>
-    <t>BUGANVILLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIWAN </t>
-  </si>
-  <si>
-    <t>SOLAR DOS OLIVEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JULIETA HOOPER </t>
-  </si>
-  <si>
-    <t>MIRANTE DO TIJUCO</t>
-  </si>
-  <si>
-    <t>BETINHA PEREIRA NEVES</t>
-  </si>
-  <si>
-    <t>PALAZZO DI LOURDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALAZZO TOSCANA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">51 GARDEN PARK </t>
-  </si>
-  <si>
-    <t>BASILEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MONT BLANC </t>
-  </si>
-  <si>
-    <t>ASS. AlPHAVILLE LAGOA DOS INGLESES</t>
-  </si>
-  <si>
-    <t>03.826.434/0001-33</t>
-  </si>
-  <si>
-    <t>TORDESILHAS</t>
-  </si>
-  <si>
-    <t>04.347.609/0001-92</t>
-  </si>
-  <si>
-    <t>CONQUISTA ALVORADA</t>
-  </si>
-  <si>
-    <t>60.345.361/0001-00</t>
-  </si>
-  <si>
-    <t>MOZART</t>
-  </si>
-  <si>
-    <t>63.966.805/0001-04</t>
-  </si>
-  <si>
-    <t>ESSENCE RESIDENCIAL</t>
-  </si>
-  <si>
-    <t>PLUS_PJ</t>
-  </si>
-  <si>
-    <t>63.300.262/0001-91</t>
-  </si>
-  <si>
-    <t>BARAO RIO VERMELHO</t>
-  </si>
-  <si>
-    <t>65.178.832/0001-48</t>
-  </si>
-  <si>
-    <t>RESIDENCIAL DAS AMERICAS</t>
-  </si>
-  <si>
-    <t>07.925.356/0001-85</t>
-  </si>
-  <si>
-    <t>VILLA FRATINA</t>
-  </si>
-  <si>
-    <t>17.642.214/0001-64</t>
-  </si>
-  <si>
-    <t>PRESIDENTE JUCELINO</t>
-  </si>
-  <si>
-    <t>02.464.572/0001-57</t>
-  </si>
-  <si>
-    <t>ALICE MOURA</t>
-  </si>
-  <si>
-    <t>25.569.351/0001-49</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>16.647.959/0001-53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAINT ROMAN </t>
+    <t>CONDOMED RIO SEG. MED. TRABALHO</t>
+  </si>
+  <si>
+    <t>CONDOMED</t>
+  </si>
+  <si>
+    <t>27.892.999/0001-87</t>
   </si>
 </sst>
 </file>
@@ -2277,10 +2252,9 @@
         <color rgb="FF000000"/>
         <name val="Arial"/>
         <family val="2"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center"/>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -2289,52 +2263,44 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
         <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <name val="Arial"/>
         <family val="2"/>
-        <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment vertical="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2350,16 +2316,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E8E96608-A336-487B-84FC-74891340A52C}" name="Tabela1" displayName="Tabela1" ref="A1:D340" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D340" xr:uid="{E8E96608-A336-487B-84FC-74891340A52C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D340">
-    <sortCondition ref="A1:A340"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:D337" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D337" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D337">
+    <sortCondition ref="A1:A337"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DC7CB960-927B-404F-9BFD-7EB561BE08EF}" name="COD" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{C7F2F3FA-FE41-430A-8616-D132549FBC6A}" name="CONDOMINIO" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{E1400085-1E0B-4233-B107-2F0AF9AF35BE}" name="GESTAO" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{169DC05C-D6FA-4603-89FB-4B04AFFB595C}" name="CNPJ" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="COD" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="CONDOMINIO" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="GESTAO" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="CNPJ" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2661,11 +2627,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B40F633-FF22-4F2F-A96C-46A2C55719BF}">
-  <dimension ref="A1:H340"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H338"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="5"/>
+    <col min="1" max="1" width="8.85546875" style="5" customWidth="1"/>
     <col min="2" max="2" width="39" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.28515625" style="6" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="6" customWidth="1"/>
@@ -2673,16 +2639,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>558</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>252</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2690,13 +2656,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>338</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2704,13 +2670,13 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>253</v>
+        <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>339</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2718,13 +2684,13 @@
         <v>7</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>547</v>
+        <v>11</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>340</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2732,13 +2698,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>341</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2746,13 +2712,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>342</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2760,13 +2726,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>343</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2774,13 +2740,13 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>566</v>
+        <v>21</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>567</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2788,13 +2754,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>568</v>
+        <v>23</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>569</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2802,13 +2768,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>564</v>
+        <v>25</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>565</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2816,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>344</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2830,13 +2796,13 @@
         <v>25</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>345</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2844,13 +2810,13 @@
         <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>346</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2858,13 +2824,13 @@
         <v>31</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>559</v>
-      </c>
       <c r="D14" s="8" t="s">
-        <v>347</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2872,13 +2838,13 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>557</v>
+        <v>36</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>348</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2886,13 +2852,13 @@
         <v>34</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>349</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2900,13 +2866,13 @@
         <v>40</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>570</v>
+        <v>40</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>571</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2914,13 +2880,13 @@
         <v>41</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>350</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2928,13 +2894,13 @@
         <v>44</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>351</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2942,13 +2908,13 @@
         <v>47</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>572</v>
+        <v>46</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>573</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2956,13 +2922,13 @@
         <v>51</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>352</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2970,13 +2936,13 @@
         <v>52</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>353</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2984,13 +2950,13 @@
         <v>57</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>354</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2998,13 +2964,13 @@
         <v>59</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>355</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3012,13 +2978,13 @@
         <v>64</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>356</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3026,13 +2992,13 @@
         <v>68</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>357</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3040,13 +3006,13 @@
         <v>69</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>358</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3054,13 +3020,13 @@
         <v>72</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>359</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3068,13 +3034,13 @@
         <v>73</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>635</v>
+        <v>64</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>360</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3082,13 +3048,13 @@
         <v>74</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>361</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3096,13 +3062,13 @@
         <v>75</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>547</v>
+        <v>11</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>362</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3110,13 +3076,13 @@
         <v>82</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>363</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3124,13 +3090,13 @@
         <v>83</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>364</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3138,13 +3104,13 @@
         <v>84</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>365</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3152,13 +3118,13 @@
         <v>90</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>366</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -3166,13 +3132,13 @@
         <v>93</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>367</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -3180,13 +3146,13 @@
         <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>368</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3194,13 +3160,13 @@
         <v>108</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>369</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3208,13 +3174,13 @@
         <v>109</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>370</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3222,13 +3188,13 @@
         <v>110</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>578</v>
+        <v>86</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>577</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3236,13 +3202,13 @@
         <v>111</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>371</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3250,13 +3216,13 @@
         <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>372</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3264,13 +3230,13 @@
         <v>113</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>373</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3278,13 +3244,13 @@
         <v>117</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>374</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3292,13 +3258,13 @@
         <v>118</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>375</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3306,13 +3272,13 @@
         <v>119</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>376</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3320,13 +3286,13 @@
         <v>121</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>377</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3334,13 +3300,13 @@
         <v>123</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>378</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3348,13 +3314,13 @@
         <v>124</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>636</v>
+        <v>106</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>379</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3362,13 +3328,13 @@
         <v>127</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>380</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3376,13 +3342,13 @@
         <v>135</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>381</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3390,13 +3356,13 @@
         <v>136</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>382</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3404,13 +3370,13 @@
         <v>137</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>383</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3418,13 +3384,13 @@
         <v>139</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>574</v>
+        <v>116</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>575</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3432,13 +3398,13 @@
         <v>142</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>581</v>
+        <v>118</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>582</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3446,13 +3412,13 @@
         <v>145</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>384</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3460,13 +3426,13 @@
         <v>146</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>385</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3474,13 +3440,13 @@
         <v>161</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>386</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3488,13 +3454,13 @@
         <v>164</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>550</v>
+        <v>126</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>547</v>
+        <v>11</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>387</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3502,13 +3468,13 @@
         <v>170</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>388</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3516,13 +3482,13 @@
         <v>172</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>389</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3530,13 +3496,13 @@
         <v>173</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>390</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3544,13 +3510,13 @@
         <v>175</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>391</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3558,13 +3524,13 @@
         <v>176</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>579</v>
+        <v>136</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>583</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3572,13 +3538,13 @@
         <v>179</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>551</v>
+        <v>138</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>392</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3586,13 +3552,13 @@
         <v>181</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>393</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3600,13 +3566,13 @@
         <v>186</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>50</v>
+        <v>142</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>394</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3614,13 +3580,13 @@
         <v>187</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>395</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3628,13 +3594,13 @@
         <v>189</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>396</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3642,13 +3608,13 @@
         <v>198</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>397</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3656,13 +3622,13 @@
         <v>200</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3670,13 +3636,13 @@
         <v>206</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>399</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3684,13 +3650,13 @@
         <v>207</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>400</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3698,13 +3664,13 @@
         <v>210</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>401</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3712,13 +3678,13 @@
         <v>216</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>402</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3726,13 +3692,13 @@
         <v>219</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>584</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3740,13 +3706,13 @@
         <v>224</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>59</v>
+        <v>162</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>403</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3754,13 +3720,13 @@
         <v>225</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>404</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3768,13 +3734,13 @@
         <v>227</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>405</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3782,13 +3748,13 @@
         <v>230</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>406</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3796,13 +3762,13 @@
         <v>231</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>63</v>
+        <v>170</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>407</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3810,13 +3776,13 @@
         <v>236</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>591</v>
+        <v>172</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>590</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3824,13 +3790,13 @@
         <v>240</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>64</v>
+        <v>174</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>408</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3838,13 +3804,13 @@
         <v>242</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>637</v>
+        <v>176</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>409</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3852,13 +3818,13 @@
         <v>245</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>585</v>
+        <v>178</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>587</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3866,13 +3832,13 @@
         <v>247</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>410</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3880,13 +3846,13 @@
         <v>248</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>586</v>
+        <v>182</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>594</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3894,13 +3860,13 @@
         <v>258</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>547</v>
+        <v>11</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>411</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3908,13 +3874,13 @@
         <v>260</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>412</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3922,13 +3888,13 @@
         <v>264</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>413</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3936,13 +3902,13 @@
         <v>274</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>588</v>
+        <v>190</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>589</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3950,13 +3916,13 @@
         <v>275</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>414</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3964,13 +3930,13 @@
         <v>276</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>70</v>
+        <v>194</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>415</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -3978,13 +3944,13 @@
         <v>278</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>593</v>
+        <v>196</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>592</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3992,13 +3958,13 @@
         <v>286</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>416</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -4006,13 +3972,13 @@
         <v>287</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>417</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -4020,13 +3986,13 @@
         <v>289</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>73</v>
+        <v>202</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>418</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -4034,13 +4000,13 @@
         <v>290</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>596</v>
+        <v>204</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>595</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -4048,13 +4014,13 @@
         <v>291</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>419</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -4062,13 +4028,13 @@
         <v>294</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>598</v>
+        <v>208</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>597</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -4076,13 +4042,13 @@
         <v>301</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>420</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -4090,13 +4056,13 @@
         <v>303</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>76</v>
+        <v>212</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>421</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -4104,13 +4070,13 @@
         <v>304</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>422</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -4118,13 +4084,13 @@
         <v>305</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>423</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -4132,13 +4098,13 @@
         <v>308</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>424</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -4146,13 +4112,13 @@
         <v>311</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>547</v>
+        <v>11</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>425</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -4160,13 +4126,13 @@
         <v>315</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>602</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -4174,13 +4140,13 @@
         <v>318</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>426</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -4188,13 +4154,13 @@
         <v>320</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>427</v>
+        <v>227</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -4202,13 +4168,13 @@
         <v>322</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>428</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -4216,13 +4182,13 @@
         <v>324</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>84</v>
+        <v>230</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>429</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -4230,13 +4196,13 @@
         <v>325</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>552</v>
+        <v>232</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>430</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -4244,13 +4210,13 @@
         <v>334</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>85</v>
+        <v>234</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>431</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -4258,13 +4224,13 @@
         <v>338</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>86</v>
+        <v>236</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>432</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -4272,13 +4238,13 @@
         <v>342</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>87</v>
+        <v>238</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>433</v>
+        <v>239</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -4286,13 +4252,13 @@
         <v>346</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>599</v>
+        <v>240</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>600</v>
+        <v>241</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -4300,13 +4266,13 @@
         <v>348</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>88</v>
+        <v>242</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>434</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -4314,13 +4280,13 @@
         <v>358</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>638</v>
+        <v>244</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>435</v>
+        <v>245</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -4328,13 +4294,13 @@
         <v>360</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>89</v>
+        <v>246</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>436</v>
+        <v>247</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -4342,13 +4308,13 @@
         <v>361</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>90</v>
+        <v>248</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>437</v>
+        <v>249</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -4356,13 +4322,13 @@
         <v>364</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>639</v>
+        <v>250</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>438</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -4370,13 +4336,13 @@
         <v>366</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>640</v>
+        <v>252</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>601</v>
+        <v>253</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -4384,13 +4350,13 @@
         <v>372</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>220</v>
+        <v>254</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>607</v>
+        <v>255</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -4398,13 +4364,13 @@
         <v>375</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>439</v>
+        <v>257</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -4412,13 +4378,13 @@
         <v>379</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>641</v>
+        <v>258</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>440</v>
+        <v>259</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -4426,13 +4392,13 @@
         <v>381</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>91</v>
+        <v>260</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>441</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -4440,13 +4406,13 @@
         <v>383</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>686</v>
+        <v>262</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>442</v>
+        <v>263</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -4454,13 +4420,13 @@
         <v>385</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>92</v>
+        <v>264</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>443</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -4468,13 +4434,13 @@
         <v>393</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>444</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -4482,13 +4448,13 @@
         <v>394</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>445</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -4496,13 +4462,13 @@
         <v>395</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>603</v>
+        <v>270</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>604</v>
+        <v>271</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -4510,13 +4476,13 @@
         <v>398</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>95</v>
+        <v>272</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>446</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -4524,13 +4490,13 @@
         <v>400</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>447</v>
+        <v>275</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -4538,13 +4504,13 @@
         <v>401</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>642</v>
+        <v>276</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D134" s="8" t="s">
-        <v>448</v>
+        <v>277</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -4552,13 +4518,13 @@
         <v>408</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>97</v>
+        <v>278</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D135" s="8" t="s">
-        <v>449</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -4566,13 +4532,13 @@
         <v>413</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>606</v>
+        <v>280</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D136" s="8" t="s">
-        <v>605</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -4580,13 +4546,13 @@
         <v>415</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>98</v>
+        <v>282</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>450</v>
+        <v>283</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -4594,13 +4560,13 @@
         <v>417</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>608</v>
+        <v>284</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>609</v>
+        <v>285</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -4608,13 +4574,13 @@
         <v>420</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>99</v>
+        <v>286</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>451</v>
+        <v>287</v>
       </c>
       <c r="H139" s="18"/>
     </row>
@@ -4623,13 +4589,13 @@
         <v>429</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>100</v>
+        <v>288</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D140" s="8" t="s">
-        <v>452</v>
+        <v>289</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -4637,13 +4603,13 @@
         <v>431</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>643</v>
+        <v>290</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>611</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -4651,13 +4617,13 @@
         <v>434</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>101</v>
+        <v>292</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D142" s="8" t="s">
-        <v>453</v>
+        <v>293</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -4665,13 +4631,13 @@
         <v>442</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>102</v>
+        <v>294</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D143" s="8" t="s">
-        <v>454</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -4679,13 +4645,13 @@
         <v>443</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>103</v>
+        <v>296</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D144" s="8" t="s">
-        <v>455</v>
+        <v>297</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4693,13 +4659,13 @@
         <v>445</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>104</v>
+        <v>298</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D145" s="8" t="s">
-        <v>456</v>
+        <v>299</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4707,13 +4673,13 @@
         <v>449</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>105</v>
+        <v>300</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>457</v>
+        <v>301</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4721,13 +4687,13 @@
         <v>456</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>644</v>
+        <v>302</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D147" s="8" t="s">
-        <v>458</v>
+        <v>303</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4735,13 +4701,13 @@
         <v>463</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>106</v>
+        <v>304</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D148" s="8" t="s">
-        <v>459</v>
+        <v>305</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4749,13 +4715,13 @@
         <v>471</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>620</v>
+        <v>306</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D149" s="8" t="s">
-        <v>621</v>
+        <v>307</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4763,13 +4729,13 @@
         <v>473</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>107</v>
+        <v>308</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>460</v>
+        <v>309</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4777,13 +4743,13 @@
         <v>475</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>108</v>
+        <v>310</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>461</v>
+        <v>311</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4791,13 +4757,13 @@
         <v>476</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>645</v>
+        <v>312</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>462</v>
+        <v>313</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4805,13 +4771,13 @@
         <v>477</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>646</v>
+        <v>314</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>463</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4819,13 +4785,13 @@
         <v>481</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>612</v>
+        <v>316</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>613</v>
+        <v>317</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4833,13 +4799,13 @@
         <v>485</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>109</v>
+        <v>318</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>464</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4847,13 +4813,13 @@
         <v>492</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D156" s="8" t="s">
-        <v>465</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -4861,13 +4827,13 @@
         <v>493</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>111</v>
+        <v>322</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D157" s="8" t="s">
-        <v>466</v>
+        <v>323</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4875,13 +4841,13 @@
         <v>499</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>112</v>
+        <v>324</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D158" s="8" t="s">
-        <v>467</v>
+        <v>325</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -4889,13 +4855,13 @@
         <v>502</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>113</v>
+        <v>326</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>468</v>
+        <v>327</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4903,13 +4869,13 @@
         <v>504</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>614</v>
+        <v>328</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D160" s="8" t="s">
-        <v>615</v>
+        <v>329</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4917,13 +4883,13 @@
         <v>506</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>114</v>
+        <v>330</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D161" s="8" t="s">
-        <v>469</v>
+        <v>331</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -4931,13 +4897,13 @@
         <v>513</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>616</v>
+        <v>332</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D162" s="8" t="s">
-        <v>617</v>
+        <v>333</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4945,13 +4911,13 @@
         <v>515</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>115</v>
+        <v>334</v>
       </c>
       <c r="C163" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>470</v>
+        <v>335</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -4959,13 +4925,13 @@
         <v>517</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>116</v>
+        <v>336</v>
       </c>
       <c r="C164" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>471</v>
+        <v>337</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -4973,13 +4939,13 @@
         <v>523</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>117</v>
+        <v>338</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D165" s="8" t="s">
-        <v>472</v>
+        <v>339</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -4987,13 +4953,13 @@
         <v>528</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>118</v>
+        <v>340</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D166" s="8" t="s">
-        <v>473</v>
+        <v>341</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -5001,13 +4967,13 @@
         <v>536</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>119</v>
+        <v>342</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>474</v>
+        <v>343</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -5015,13 +4981,13 @@
         <v>539</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>120</v>
+        <v>344</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>475</v>
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -5029,13 +4995,13 @@
         <v>544</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>121</v>
+        <v>346</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>476</v>
+        <v>347</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -5043,13 +5009,13 @@
         <v>554</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>122</v>
+        <v>348</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>477</v>
+        <v>349</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -5057,13 +5023,13 @@
         <v>560</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>123</v>
+        <v>350</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>478</v>
+        <v>351</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -5071,13 +5037,13 @@
         <v>566</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>124</v>
+        <v>352</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D172" s="8" t="s">
-        <v>479</v>
+        <v>353</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -5085,13 +5051,13 @@
         <v>573</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>125</v>
+        <v>354</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D173" s="8" t="s">
-        <v>480</v>
+        <v>355</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -5099,13 +5065,13 @@
         <v>580</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>553</v>
+        <v>356</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>481</v>
+        <v>357</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -5113,13 +5079,13 @@
         <v>582</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>618</v>
+        <v>358</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>619</v>
+        <v>359</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -5127,13 +5093,13 @@
         <v>586</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>126</v>
+        <v>360</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>482</v>
+        <v>361</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -5141,13 +5107,13 @@
         <v>589</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>647</v>
+        <v>362</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>624</v>
+        <v>363</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -5155,13 +5121,13 @@
         <v>591</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>127</v>
+        <v>364</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>483</v>
+        <v>365</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -5169,13 +5135,13 @@
         <v>592</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>128</v>
+        <v>366</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>484</v>
+        <v>367</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -5183,13 +5149,13 @@
         <v>593</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>648</v>
+        <v>368</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>485</v>
+        <v>369</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -5197,13 +5163,13 @@
         <v>594</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>129</v>
+        <v>370</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>486</v>
+        <v>371</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -5211,13 +5177,13 @@
         <v>595</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>649</v>
+        <v>372</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>487</v>
+        <v>373</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -5225,13 +5191,13 @@
         <v>604</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>130</v>
+        <v>374</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>488</v>
+        <v>375</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -5239,13 +5205,13 @@
         <v>605</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>131</v>
+        <v>376</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>489</v>
+        <v>377</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -5253,13 +5219,13 @@
         <v>610</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>132</v>
+        <v>378</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>490</v>
+        <v>379</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -5267,13 +5233,13 @@
         <v>611</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>133</v>
+        <v>380</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D186" s="8" t="s">
-        <v>491</v>
+        <v>381</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -5281,13 +5247,13 @@
         <v>613</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>134</v>
+        <v>382</v>
       </c>
       <c r="C187" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D187" s="8" t="s">
-        <v>492</v>
+        <v>383</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -5295,13 +5261,13 @@
         <v>614</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>650</v>
+        <v>384</v>
       </c>
       <c r="C188" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D188" s="8" t="s">
-        <v>493</v>
+        <v>385</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -5309,13 +5275,13 @@
         <v>618</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>651</v>
+        <v>386</v>
       </c>
       <c r="C189" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D189" s="8" t="s">
-        <v>494</v>
+        <v>387</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -5323,13 +5289,13 @@
         <v>619</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>135</v>
+        <v>388</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D190" s="8" t="s">
-        <v>495</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -5337,13 +5303,13 @@
         <v>626</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>136</v>
+        <v>390</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D191" s="8" t="s">
-        <v>496</v>
+        <v>391</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -5351,13 +5317,13 @@
         <v>628</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>137</v>
+        <v>392</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D192" s="8" t="s">
-        <v>497</v>
+        <v>393</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -5365,13 +5331,13 @@
         <v>629</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>138</v>
+        <v>394</v>
       </c>
       <c r="C193" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D193" s="8" t="s">
-        <v>498</v>
+        <v>395</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -5379,13 +5345,13 @@
         <v>631</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>554</v>
+        <v>396</v>
       </c>
       <c r="C194" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>499</v>
+        <v>397</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -5393,13 +5359,13 @@
         <v>635</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>622</v>
+        <v>398</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D195" s="8" t="s">
-        <v>623</v>
+        <v>399</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -5407,13 +5373,13 @@
         <v>636</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>625</v>
+        <v>400</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="D196" s="8" t="s">
-        <v>626</v>
+        <v>401</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -5421,13 +5387,13 @@
         <v>640</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>139</v>
+        <v>402</v>
       </c>
       <c r="C197" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>500</v>
+        <v>403</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -5435,13 +5401,13 @@
         <v>641</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>627</v>
+        <v>404</v>
       </c>
       <c r="C198" s="11" t="s">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>628</v>
+        <v>405</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -5449,13 +5415,13 @@
         <v>642</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>631</v>
+        <v>406</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>632</v>
+        <v>407</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -5463,13 +5429,13 @@
         <v>647</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>652</v>
+        <v>408</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>501</v>
+        <v>409</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -5477,13 +5443,13 @@
         <v>653</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>140</v>
+        <v>410</v>
       </c>
       <c r="C201" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>502</v>
+        <v>411</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -5491,13 +5457,13 @@
         <v>654</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>629</v>
+        <v>412</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>630</v>
+        <v>413</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -5505,13 +5471,13 @@
         <v>655</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>141</v>
+        <v>414</v>
       </c>
       <c r="C203" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>503</v>
+        <v>415</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -5519,13 +5485,13 @@
         <v>661</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>142</v>
+        <v>416</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>504</v>
+        <v>417</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5533,13 +5499,13 @@
         <v>662</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>143</v>
+        <v>418</v>
       </c>
       <c r="C205" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>505</v>
+        <v>419</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -5547,13 +5513,13 @@
         <v>668</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>144</v>
+        <v>420</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>506</v>
+        <v>421</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -5561,13 +5527,13 @@
         <v>675</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>663</v>
+        <v>422</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>664</v>
+        <v>423</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -5575,13 +5541,13 @@
         <v>679</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>653</v>
+        <v>424</v>
       </c>
       <c r="C208" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>507</v>
+        <v>425</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -5589,13 +5555,13 @@
         <v>681</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>555</v>
+        <v>426</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>508</v>
+        <v>427</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -5603,13 +5569,13 @@
         <v>683</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>145</v>
+        <v>428</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>509</v>
+        <v>429</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -5617,13 +5583,13 @@
         <v>689</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>146</v>
+        <v>430</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>510</v>
+        <v>431</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -5631,13 +5597,13 @@
         <v>695</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>576</v>
+        <v>432</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>511</v>
+        <v>433</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5645,13 +5611,13 @@
         <v>698</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>147</v>
+        <v>434</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>512</v>
+        <v>435</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5659,13 +5625,13 @@
         <v>700</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>148</v>
+        <v>436</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>513</v>
+        <v>437</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5673,13 +5639,13 @@
         <v>701</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>149</v>
+        <v>438</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>514</v>
+        <v>439</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5687,13 +5653,13 @@
         <v>702</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>150</v>
+        <v>440</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>515</v>
+        <v>441</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5701,13 +5667,13 @@
         <v>703</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>151</v>
+        <v>442</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>516</v>
+        <v>443</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5715,13 +5681,13 @@
         <v>704</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>152</v>
+        <v>444</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>517</v>
+        <v>445</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5729,13 +5695,13 @@
         <v>706</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>153</v>
+        <v>446</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>518</v>
+        <v>447</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5743,13 +5709,13 @@
         <v>708</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>154</v>
+        <v>448</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>519</v>
+        <v>449</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5757,13 +5723,13 @@
         <v>710</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>155</v>
+        <v>450</v>
       </c>
       <c r="C221" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>520</v>
+        <v>451</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5771,13 +5737,13 @@
         <v>711</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>156</v>
+        <v>452</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>521</v>
+        <v>453</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5785,13 +5751,13 @@
         <v>713</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>157</v>
+        <v>454</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>522</v>
+        <v>455</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5799,13 +5765,13 @@
         <v>714</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>158</v>
+        <v>456</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>523</v>
+        <v>457</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5813,13 +5779,13 @@
         <v>715</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>159</v>
+        <v>458</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>524</v>
+        <v>459</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5827,13 +5793,13 @@
         <v>716</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="C226" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>525</v>
+        <v>461</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5841,13 +5807,13 @@
         <v>717</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>161</v>
+        <v>462</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>526</v>
+        <v>463</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5855,13 +5821,13 @@
         <v>718</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="C228" s="9" t="s">
-        <v>560</v>
+        <v>89</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>527</v>
+        <v>465</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5869,13 +5835,13 @@
         <v>720</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>163</v>
+        <v>466</v>
       </c>
       <c r="C229" s="11" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>528</v>
+        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5883,13 +5849,13 @@
         <v>721</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>164</v>
+        <v>468</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>529</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5897,13 +5863,13 @@
         <v>722</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>165</v>
+        <v>470</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>530</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5911,13 +5877,13 @@
         <v>723</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>166</v>
+        <v>472</v>
       </c>
       <c r="C232" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>531</v>
+        <v>473</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5925,13 +5891,13 @@
         <v>724</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>167</v>
+        <v>474</v>
       </c>
       <c r="C233" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>532</v>
+        <v>475</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -5939,13 +5905,13 @@
         <v>731</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>168</v>
+        <v>476</v>
       </c>
       <c r="C234" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>533</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5953,13 +5919,13 @@
         <v>732</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="C235" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D235" s="8" t="s">
-        <v>534</v>
+        <v>478</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -5967,13 +5933,13 @@
         <v>737</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>169</v>
+        <v>479</v>
       </c>
       <c r="C236" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>535</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -5981,13 +5947,13 @@
         <v>738</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>170</v>
+        <v>481</v>
       </c>
       <c r="C237" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>536</v>
+        <v>482</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5995,13 +5961,13 @@
         <v>745</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>171</v>
+        <v>483</v>
       </c>
       <c r="C238" s="9" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>537</v>
+        <v>484</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -6009,13 +5975,13 @@
         <v>746</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>172</v>
+        <v>485</v>
       </c>
       <c r="C239" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>538</v>
+        <v>486</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -6023,13 +5989,13 @@
         <v>747</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>654</v>
+        <v>487</v>
       </c>
       <c r="C240" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>539</v>
+        <v>488</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -6037,13 +6003,13 @@
         <v>748</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>173</v>
+        <v>489</v>
       </c>
       <c r="C241" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>540</v>
+        <v>490</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -6051,13 +6017,13 @@
         <v>750</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>174</v>
+        <v>491</v>
       </c>
       <c r="C242" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>541</v>
+        <v>492</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -6065,13 +6031,13 @@
         <v>754</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>175</v>
+        <v>493</v>
       </c>
       <c r="C243" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>542</v>
+        <v>494</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -6079,13 +6045,13 @@
         <v>755</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>176</v>
+        <v>495</v>
       </c>
       <c r="C244" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>543</v>
+        <v>496</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -6093,13 +6059,13 @@
         <v>756</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>177</v>
+        <v>497</v>
       </c>
       <c r="C245" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>544</v>
+        <v>498</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -6107,13 +6073,13 @@
         <v>759</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>178</v>
+        <v>499</v>
       </c>
       <c r="C246" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>254</v>
+        <v>500</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -6121,13 +6087,13 @@
         <v>762</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>179</v>
+        <v>501</v>
       </c>
       <c r="C247" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>255</v>
+        <v>502</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -6135,13 +6101,13 @@
         <v>763</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>180</v>
+        <v>503</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>256</v>
+        <v>504</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -6149,13 +6115,13 @@
         <v>767</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>667</v>
+        <v>505</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>668</v>
+        <v>506</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -6163,13 +6129,13 @@
         <v>780</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>181</v>
+        <v>507</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>257</v>
+        <v>508</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -6177,13 +6143,13 @@
         <v>783</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>182</v>
+        <v>509</v>
       </c>
       <c r="C251" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>258</v>
+        <v>510</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -6191,13 +6157,13 @@
         <v>784</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>669</v>
+        <v>511</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>670</v>
+        <v>512</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -6205,13 +6171,13 @@
         <v>787</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>183</v>
+        <v>513</v>
       </c>
       <c r="C253" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>259</v>
+        <v>514</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -6219,13 +6185,13 @@
         <v>791</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>556</v>
+        <v>515</v>
       </c>
       <c r="C254" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>260</v>
+        <v>516</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -6233,13 +6199,13 @@
         <v>792</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>671</v>
+        <v>517</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>672</v>
+        <v>518</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>673</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -6247,13 +6213,13 @@
         <v>793</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>184</v>
+        <v>520</v>
       </c>
       <c r="C256" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>261</v>
+        <v>521</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -6261,13 +6227,13 @@
         <v>797</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>665</v>
+        <v>522</v>
       </c>
       <c r="C257" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>666</v>
+        <v>523</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -6275,13 +6241,13 @@
         <v>799</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>185</v>
+        <v>524</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>262</v>
+        <v>525</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -6289,13 +6255,13 @@
         <v>801</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>655</v>
+        <v>526</v>
       </c>
       <c r="C259" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>263</v>
+        <v>527</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -6303,13 +6269,13 @@
         <v>805</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>186</v>
+        <v>528</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>264</v>
+        <v>529</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -6317,13 +6283,13 @@
         <v>807</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>187</v>
+        <v>530</v>
       </c>
       <c r="C261" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>265</v>
+        <v>531</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -6331,13 +6297,13 @@
         <v>809</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>674</v>
+        <v>532</v>
       </c>
       <c r="C262" s="11" t="s">
-        <v>672</v>
+        <v>518</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>675</v>
+        <v>533</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -6345,13 +6311,13 @@
         <v>810</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>188</v>
+        <v>534</v>
       </c>
       <c r="C263" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>266</v>
+        <v>535</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -6359,13 +6325,13 @@
         <v>811</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>676</v>
+        <v>536</v>
       </c>
       <c r="C264" s="11" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>677</v>
+        <v>537</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -6373,13 +6339,13 @@
         <v>812</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>189</v>
+        <v>538</v>
       </c>
       <c r="C265" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>267</v>
+        <v>539</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -6387,13 +6353,13 @@
         <v>815</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>190</v>
+        <v>540</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>268</v>
+        <v>541</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -6401,13 +6367,13 @@
         <v>818</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>191</v>
+        <v>542</v>
       </c>
       <c r="C267" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>269</v>
+        <v>543</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6415,13 +6381,13 @@
         <v>819</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>192</v>
+        <v>544</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>270</v>
+        <v>545</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6429,13 +6395,13 @@
         <v>821</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>678</v>
+        <v>546</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D269" s="8" t="s">
-        <v>679</v>
+        <v>547</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6443,13 +6409,13 @@
         <v>824</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>610</v>
+        <v>548</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D270" s="8" t="s">
-        <v>271</v>
+        <v>549</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -6457,13 +6423,13 @@
         <v>826</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>193</v>
+        <v>550</v>
       </c>
       <c r="C271" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>272</v>
+        <v>551</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -6471,13 +6437,13 @@
         <v>828</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>194</v>
+        <v>552</v>
       </c>
       <c r="C272" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>273</v>
+        <v>553</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6485,958 +6451,930 @@
         <v>830</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>656</v>
+        <v>554</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>559</v>
+        <v>8</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>274</v>
+        <v>555</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="20">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>680</v>
+        <v>556</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>546</v>
+        <v>8</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>681</v>
+        <v>557</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="20">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="C275" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D275" s="8" t="s">
         <v>559</v>
-      </c>
-      <c r="D275" s="8" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="20">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="C276" s="12" t="s">
-        <v>546</v>
+        <v>560</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>683</v>
+        <v>561</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="20">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>195</v>
+        <v>562</v>
       </c>
       <c r="C277" s="9" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>276</v>
+        <v>563</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="20">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>196</v>
+        <v>564</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>277</v>
+        <v>565</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="20">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>197</v>
+        <v>566</v>
       </c>
       <c r="C279" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>278</v>
+        <v>567</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="20">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>198</v>
+        <v>568</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>548</v>
+        <v>5</v>
       </c>
       <c r="D280" s="8" t="s">
-        <v>279</v>
+        <v>569</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="20">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>199</v>
+        <v>570</v>
       </c>
       <c r="C281" s="9" t="s">
-        <v>548</v>
+        <v>16</v>
       </c>
       <c r="D281" s="8" t="s">
-        <v>280</v>
+        <v>571</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="20">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>200</v>
+        <v>572</v>
       </c>
       <c r="C282" s="9" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>281</v>
+        <v>573</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="20">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>201</v>
+        <v>574</v>
       </c>
       <c r="C283" s="9" t="s">
-        <v>563</v>
+        <v>19</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>282</v>
+        <v>575</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="20">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>202</v>
+        <v>576</v>
       </c>
       <c r="C284" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D284" s="8" t="s">
-        <v>283</v>
+        <v>577</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="20">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>658</v>
+        <v>578</v>
       </c>
       <c r="C285" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D285" s="8" t="s">
-        <v>284</v>
+        <v>579</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="20">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>203</v>
+        <v>580</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D286" s="8" t="s">
-        <v>285</v>
+        <v>581</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="20">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="C287" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>286</v>
+        <v>582</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="20">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>659</v>
+        <v>583</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>548</v>
+        <v>5</v>
       </c>
       <c r="D288" s="8" t="s">
-        <v>287</v>
+        <v>584</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="20">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C289" s="9" t="s">
-        <v>548</v>
+        <v>585</v>
+      </c>
+      <c r="C289" s="11" t="s">
+        <v>5</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>288</v>
+        <v>586</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="20">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>206</v>
+        <v>587</v>
       </c>
       <c r="C290" s="9" t="s">
-        <v>546</v>
+        <v>16</v>
       </c>
       <c r="D290" s="8" t="s">
-        <v>289</v>
+        <v>588</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="20">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C291" s="11" t="s">
-        <v>546</v>
+        <v>589</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>290</v>
+        <v>590</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="20">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C292" s="11" t="s">
-        <v>546</v>
+        <v>591</v>
+      </c>
+      <c r="C292" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="D292" s="8" t="s">
-        <v>685</v>
+        <v>592</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="20">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C293" s="9" t="s">
-        <v>563</v>
+        <v>593</v>
+      </c>
+      <c r="C293" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="D293" s="8" t="s">
-        <v>291</v>
+        <v>594</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="20">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>209</v>
+        <v>595</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="D294" s="8" t="s">
-        <v>292</v>
+        <v>596</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="20">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C295" s="12" t="s">
-        <v>559</v>
+        <v>597</v>
+      </c>
+      <c r="C295" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="D295" s="8" t="s">
-        <v>293</v>
+        <v>598</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="20">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C296" s="12" t="s">
-        <v>559</v>
+        <v>599</v>
+      </c>
+      <c r="C296" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>294</v>
+        <v>600</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="20">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>212</v>
+        <v>601</v>
       </c>
       <c r="C297" s="9" t="s">
-        <v>548</v>
+        <v>19</v>
       </c>
       <c r="D297" s="8" t="s">
-        <v>295</v>
+        <v>602</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="20">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>213</v>
+        <v>603</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>563</v>
+        <v>19</v>
       </c>
       <c r="D298" s="8" t="s">
-        <v>296</v>
+        <v>604</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="20">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>214</v>
+        <v>605</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>563</v>
+        <v>5</v>
       </c>
       <c r="D299" s="8" t="s">
-        <v>297</v>
+        <v>606</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="20">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>215</v>
+        <v>607</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>548</v>
+        <v>89</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>298</v>
+        <v>608</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="20">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C301" s="9" t="s">
-        <v>548</v>
+        <v>609</v>
+      </c>
+      <c r="C301" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="D301" s="8" t="s">
-        <v>299</v>
+        <v>610</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="20">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C302" s="9" t="s">
-        <v>546</v>
+        <v>254</v>
+      </c>
+      <c r="C302" s="11" t="s">
+        <v>5</v>
       </c>
       <c r="D302" s="8" t="s">
-        <v>300</v>
+        <v>611</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="20">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>218</v>
+        <v>612</v>
       </c>
       <c r="C303" s="9" t="s">
-        <v>560</v>
+        <v>16</v>
       </c>
       <c r="D303" s="8" t="s">
-        <v>301</v>
+        <v>613</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="20">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C304" s="12" t="s">
-        <v>559</v>
+        <v>614</v>
+      </c>
+      <c r="C304" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="D304" s="8" t="s">
-        <v>302</v>
+        <v>615</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="20">
-        <v>892</v>
+        <v>902</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C305" s="11" t="s">
-        <v>546</v>
+        <v>616</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="D305" s="8" t="s">
-        <v>303</v>
+        <v>617</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="20">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>221</v>
+        <v>618</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>563</v>
+        <v>5</v>
       </c>
       <c r="D306" s="8" t="s">
-        <v>304</v>
+        <v>619</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="20">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>222</v>
+        <v>620</v>
       </c>
       <c r="C307" s="9" t="s">
-        <v>548</v>
+        <v>5</v>
       </c>
       <c r="D307" s="8" t="s">
-        <v>305</v>
+        <v>621</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="20">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>223</v>
+        <v>622</v>
       </c>
       <c r="C308" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D308" s="8" t="s">
-        <v>306</v>
+        <v>623</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="20">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>224</v>
+        <v>624</v>
       </c>
       <c r="C309" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D309" s="8" t="s">
-        <v>307</v>
+        <v>625</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="20">
-        <v>910</v>
+        <v>924</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>225</v>
+        <v>626</v>
       </c>
       <c r="C310" s="9" t="s">
-        <v>546</v>
+        <v>16</v>
       </c>
       <c r="D310" s="8" t="s">
-        <v>308</v>
+        <v>627</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="20">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>226</v>
+        <v>628</v>
       </c>
       <c r="C311" s="9" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="D311" s="8" t="s">
-        <v>309</v>
+        <v>629</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="20">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C312" s="9" t="s">
-        <v>546</v>
+        <v>630</v>
+      </c>
+      <c r="C312" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="D312" s="8" t="s">
-        <v>310</v>
+        <v>631</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="20">
-        <v>924</v>
+        <v>937</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>228</v>
+        <v>632</v>
       </c>
       <c r="C313" s="9" t="s">
-        <v>563</v>
+        <v>16</v>
       </c>
       <c r="D313" s="8" t="s">
-        <v>311</v>
+        <v>633</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="20">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>229</v>
+        <v>634</v>
       </c>
       <c r="C314" s="9" t="s">
-        <v>548</v>
+        <v>5</v>
       </c>
       <c r="D314" s="8" t="s">
-        <v>312</v>
+        <v>635</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="20">
-        <v>927</v>
+        <v>942</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C315" s="12" t="s">
-        <v>559</v>
+        <v>636</v>
+      </c>
+      <c r="C315" s="9" t="s">
+        <v>637</v>
       </c>
       <c r="D315" s="8" t="s">
-        <v>313</v>
+        <v>638</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="20">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>231</v>
+        <v>499</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>563</v>
+        <v>5</v>
       </c>
       <c r="D316" s="8" t="s">
-        <v>314</v>
+        <v>639</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="20">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>232</v>
+        <v>640</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D317" s="8" t="s">
-        <v>315</v>
+        <v>641</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="20">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="C318" s="9" t="s">
-        <v>562</v>
+        <v>19</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>316</v>
+        <v>643</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="20">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>178</v>
+        <v>644</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>546</v>
+        <v>19</v>
       </c>
       <c r="D319" s="8" t="s">
-        <v>317</v>
+        <v>645</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="20">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="C320" s="9" t="s">
-        <v>546</v>
+        <v>16</v>
       </c>
       <c r="D320" s="8" t="s">
-        <v>318</v>
+        <v>647</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="20">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>233</v>
+        <v>648</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>548</v>
+        <v>5</v>
       </c>
       <c r="D321" s="8" t="s">
-        <v>319</v>
+        <v>649</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="20">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="C322" s="9" t="s">
-        <v>548</v>
+        <v>650</v>
+      </c>
+      <c r="C322" s="15" t="s">
+        <v>5</v>
       </c>
       <c r="D322" s="8" t="s">
-        <v>320</v>
+        <v>651</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="20">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>235</v>
+        <v>652</v>
       </c>
       <c r="C323" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="D323" s="8" t="s">
-        <v>321</v>
+        <v>5</v>
+      </c>
+      <c r="D323" s="13" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="20">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="C324" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="D324" s="8" t="s">
-        <v>322</v>
+        <v>19</v>
+      </c>
+      <c r="D324" s="13" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="20">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C325" s="15" t="s">
-        <v>546</v>
-      </c>
-      <c r="D325" s="8" t="s">
-        <v>323</v>
+        <v>655</v>
+      </c>
+      <c r="C325" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" s="13" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="20">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C326" s="9" t="s">
-        <v>546</v>
+        <v>657</v>
+      </c>
+      <c r="C326" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D326" s="13" t="s">
-        <v>324</v>
+        <v>658</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="20">
-        <v>959</v>
+        <v>968</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C327" s="9" t="s">
-        <v>548</v>
+        <v>659</v>
+      </c>
+      <c r="C327" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="D327" s="13" t="s">
-        <v>325</v>
+        <v>660</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="20">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C328" s="9" t="s">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="D328" s="13" t="s">
-        <v>326</v>
+        <v>662</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="20">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="C329" s="16" t="s">
-        <v>546</v>
+        <v>663</v>
+      </c>
+      <c r="C329" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="D329" s="13" t="s">
-        <v>327</v>
+        <v>664</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="20">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C330" s="16" t="s">
-        <v>563</v>
+        <v>665</v>
+      </c>
+      <c r="C330" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="D330" s="13" t="s">
-        <v>328</v>
+        <v>666</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="20">
-        <v>972</v>
+        <v>985</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C331" s="9" t="s">
-        <v>546</v>
+        <v>667</v>
+      </c>
+      <c r="C331" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="D331" s="13" t="s">
-        <v>329</v>
+        <v>668</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="20">
-        <v>975</v>
+        <v>989</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>241</v>
+        <v>669</v>
       </c>
       <c r="C332" s="9" t="s">
-        <v>546</v>
+        <v>16</v>
       </c>
       <c r="D332" s="13" t="s">
-        <v>330</v>
+        <v>670</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="20">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C333" s="9" t="s">
-        <v>548</v>
+        <v>671</v>
+      </c>
+      <c r="C333" s="19" t="s">
+        <v>8</v>
       </c>
       <c r="D333" s="13" t="s">
-        <v>331</v>
+        <v>672</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="20">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C334" s="16" t="s">
-        <v>548</v>
+        <v>673</v>
+      </c>
+      <c r="C334" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="D334" s="13" t="s">
-        <v>332</v>
+        <v>674</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="20">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C335" s="9" t="s">
-        <v>563</v>
+        <v>675</v>
+      </c>
+      <c r="C335" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="D335" s="13" t="s">
-        <v>333</v>
+        <v>676</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="20">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C336" s="19" t="s">
-        <v>559</v>
+        <v>677</v>
+      </c>
+      <c r="C336" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="D336" s="13" t="s">
-        <v>334</v>
+        <v>678</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="20">
-        <v>991</v>
+        <v>4006</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C337" s="9" t="s">
-        <v>548</v>
+        <v>679</v>
+      </c>
+      <c r="C337" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="D337" s="13" t="s">
-        <v>335</v>
+        <v>680</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A338" s="20">
-        <v>996</v>
-      </c>
-      <c r="B338" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C338" s="16" t="s">
-        <v>548</v>
-      </c>
-      <c r="D338" s="13" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A339" s="20">
-        <v>998</v>
-      </c>
-      <c r="B339" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C339" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="D339" s="13" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="20">
-        <v>4006</v>
-      </c>
-      <c r="B340" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C340" s="16" t="s">
-        <v>563</v>
-      </c>
-      <c r="D340" s="13" t="s">
-        <v>545</v>
+      <c r="A338">
+        <v>999</v>
+      </c>
+      <c r="B338" t="s">
+        <v>681</v>
+      </c>
+      <c r="C338" t="s">
+        <v>682</v>
+      </c>
+      <c r="D338" t="s">
+        <v>683</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>